--- a/MDK-ARM/F401RC_analysis.xlsx
+++ b/MDK-ARM/F401RC_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="116">
   <si>
     <t>F401RC</t>
   </si>
@@ -26,10 +26,13 @@
     <t>usart_idel_config.o</t>
   </si>
   <si>
+    <t>usart.o</t>
+  </si>
+  <si>
     <t>spi.o</t>
   </si>
   <si>
-    <t>usart.o</t>
+    <t>st7789.o</t>
   </si>
   <si>
     <t>i2c.o</t>
@@ -50,28 +53,52 @@
     <t>system_stm32f4xx.o</t>
   </si>
   <si>
+    <t>w25qxx.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal_i2c.o</t>
   </si>
   <si>
     <t>stm32f4xx_hal_uart.o</t>
   </si>
   <si>
+    <t>btod.o</t>
+  </si>
+  <si>
+    <t>stm32f4xx_hal_spi.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal_rcc.o</t>
   </si>
   <si>
+    <t>_printf_fp_dec.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal_dma.o</t>
   </si>
   <si>
+    <t>_printf_fp_hex.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal_tim.o</t>
   </si>
   <si>
-    <t>stm32f4xx_hal_spi.o</t>
+    <t>main.o</t>
   </si>
   <si>
     <t>stm32f4xx_hal_gpio.o</t>
   </si>
   <si>
-    <t>main.o</t>
+    <t>__printf_flags_ss_wp.o</t>
+  </si>
+  <si>
+    <t>bigflt0.o</t>
+  </si>
+  <si>
+    <t>_scanf_int.o</t>
+  </si>
+  <si>
+    <t>lc_ctype_c.o</t>
   </si>
   <si>
     <t>gpio.o</t>
@@ -80,33 +107,102 @@
     <t>lludivv7m.o</t>
   </si>
   <si>
+    <t>_printf_wctomb.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal_cortex.o</t>
   </si>
   <si>
+    <t>_printf_hex_int_ll_ptr.o</t>
+  </si>
+  <si>
+    <t>_printf_intcommon.o</t>
+  </si>
+  <si>
+    <t>lludiv10.o</t>
+  </si>
+  <si>
+    <t>_printf_fp_infnan.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_it.o</t>
   </si>
   <si>
+    <t>strcmpv7em.o</t>
+  </si>
+  <si>
+    <t>_printf_longlong_dec.o</t>
+  </si>
+  <si>
     <t>dma.o</t>
   </si>
   <si>
+    <t>_printf_dec.o</t>
+  </si>
+  <si>
+    <t>_printf_oct_int_ll.o</t>
+  </si>
+  <si>
     <t>__scatter.o</t>
   </si>
   <si>
+    <t>_printf_str.o</t>
+  </si>
+  <si>
     <t>rt_memclr_w.o</t>
   </si>
   <si>
+    <t>_printf_pad.o</t>
+  </si>
+  <si>
     <t>sys_stackheap_outer.o</t>
   </si>
   <si>
+    <t>lc_numeric_c.o</t>
+  </si>
+  <si>
+    <t>_c16rtomb.o</t>
+  </si>
+  <si>
+    <t>vsnprintf.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal_msp.o</t>
   </si>
   <si>
+    <t>m_wm.l</t>
+  </si>
+  <si>
+    <t>fpclassify.o</t>
+  </si>
+  <si>
+    <t>_printf_char_common.o</t>
+  </si>
+  <si>
+    <t>_printf_wchar.o</t>
+  </si>
+  <si>
+    <t>_printf_char.o</t>
+  </si>
+  <si>
+    <t>_printf_charcount.o</t>
+  </si>
+  <si>
+    <t>_printf_truncate.o</t>
+  </si>
+  <si>
+    <t>fz_wm.l</t>
+  </si>
+  <si>
+    <t>libinit2.o</t>
+  </si>
+  <si>
+    <t>_chval.o</t>
+  </si>
+  <si>
     <t>__scatter_zi.o</t>
   </si>
   <si>
-    <t>fz_wm.l</t>
-  </si>
-  <si>
     <t>fpinit.o</t>
   </si>
   <si>
@@ -116,6 +212,15 @@
     <t>exit.o</t>
   </si>
   <si>
+    <t>rt_ctype_table.o</t>
+  </si>
+  <si>
+    <t>_snputc.o</t>
+  </si>
+  <si>
+    <t>__printf_wp.o</t>
+  </si>
+  <si>
     <t>sys_exit.o</t>
   </si>
   <si>
@@ -125,16 +230,91 @@
     <t>rtexit2.o</t>
   </si>
   <si>
+    <t>_printf_ll.o</t>
+  </si>
+  <si>
+    <t>_printf_l.o</t>
+  </si>
+  <si>
+    <t>rt_locale_intlibspace.o</t>
+  </si>
+  <si>
     <t>__main.o</t>
   </si>
   <si>
-    <t>libinit2.o</t>
-  </si>
-  <si>
     <t>heapauxi.o</t>
   </si>
   <si>
+    <t>_printf_x.o</t>
+  </si>
+  <si>
+    <t>_printf_u.o</t>
+  </si>
+  <si>
+    <t>_printf_s.o</t>
+  </si>
+  <si>
+    <t>_printf_p.o</t>
+  </si>
+  <si>
+    <t>_printf_o.o</t>
+  </si>
+  <si>
+    <t>_printf_n.o</t>
+  </si>
+  <si>
+    <t>_printf_ls.o</t>
+  </si>
+  <si>
+    <t>_printf_llx.o</t>
+  </si>
+  <si>
+    <t>_printf_llu.o</t>
+  </si>
+  <si>
+    <t>_printf_llo.o</t>
+  </si>
+  <si>
+    <t>_printf_lli.o</t>
+  </si>
+  <si>
+    <t>_printf_lld.o</t>
+  </si>
+  <si>
+    <t>_printf_lc.o</t>
+  </si>
+  <si>
+    <t>_printf_i.o</t>
+  </si>
+  <si>
+    <t>_printf_g.o</t>
+  </si>
+  <si>
+    <t>_printf_f.o</t>
+  </si>
+  <si>
+    <t>_printf_e.o</t>
+  </si>
+  <si>
+    <t>_printf_d.o</t>
+  </si>
+  <si>
+    <t>_printf_c.o</t>
+  </si>
+  <si>
+    <t>_printf_a.o</t>
+  </si>
+  <si>
     <t>__rtentry4.o</t>
+  </si>
+  <si>
+    <t>printf2.o</t>
+  </si>
+  <si>
+    <t>printf1.o</t>
+  </si>
+  <si>
+    <t>_printf_percent_end.o</t>
   </si>
   <si>
     <t>stm32f4xx_hal_tim_ex.o</t>
@@ -272,9 +452,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$48</c:f>
+              <c:f>ram_percent!$A$3:$A$108</c:f>
               <c:strCache>
-                <c:ptCount val="46"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>startup_stm32f401xc.o</c:v>
                 </c:pt>
@@ -282,30 +462,36 @@
                   <c:v>usart_idel_config.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>usart.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>usart.o</c:v>
-                </c:pt>
                 <c:pt idx="4">
+                  <c:v>st7789.o</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>c_w.l</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="11">
+                  <c:v>w25qxx.o</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -313,41 +499,47 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$48</c:f>
+              <c:f>ram_percent!$B$3:$B$108</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
-                  <c:v>41.3681640625</c:v>
+                  <c:v>37.26346588134766</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.57877731323242</c:v>
+                  <c:v>24.86656951904297</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.695663452148438</c:v>
+                  <c:v>11.79039287567139</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.049285888671875</c:v>
+                  <c:v>8.733624458312988</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.847831726074219</c:v>
+                  <c:v>6.234837532043457</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.58551025390625</c:v>
+                  <c:v>4.366812229156494</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.58551025390625</c:v>
+                  <c:v>2.328966617584229</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.939132809638977</c:v>
+                  <c:v>2.328966617584229</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2423916012048721</c:v>
+                  <c:v>1.746724843978882</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1077295988798142</c:v>
-                </c:pt>
-                <c:pt idx="45">
+                  <c:v>0.2183406054973602</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.09704027324914932</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.02426006831228733</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -415,145 +607,325 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$48</c:f>
+              <c:f>flash_percent!$A$3:$A$108</c:f>
               <c:strCache>
-                <c:ptCount val="46"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
+                  <c:v>c_w.l</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>stm32f4xx_hal_i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>st7789.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>stm32f4xx_hal_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>btod.o</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>stm32f4xx_hal_spi.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>stm32f4xx_hal_rcc.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="7">
+                  <c:v>_printf_fp_dec.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>stm32f4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="9">
+                  <c:v>_printf_fp_hex.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>stm32f4xx_hal_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="11">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>c_w.l</c:v>
-                </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="12">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>stm32f4xx_hal_spi.o</c:v>
-                </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="13">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>startup_stm32f401xc.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="15">
                   <c:v>stm32f4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>main.o</c:v>
-                </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="16">
+                  <c:v>__printf_flags_ss_wp.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>bigflt0.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>_scanf_int.o</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>lc_ctype_c.o</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>w25qxx.o</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="22">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="23">
                   <c:v>lludivv7m.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="24">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="25">
                   <c:v>usart_idel_config.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="26">
+                  <c:v>_printf_wctomb.o</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>stm32f4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="28">
+                  <c:v>_printf_hex_int_ll_ptr.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>_printf_intcommon.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>lludiv10.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>_printf_fp_infnan.o</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="33">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="34">
+                  <c:v>strcmpv7em.o</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>_printf_longlong_dec.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="37">
+                  <c:v>_printf_dec.o</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>_printf_oct_int_ll.o</c:v>
+                </c:pt>
+                <c:pt idx="39">
                   <c:v>__scatter.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="40">
+                  <c:v>_printf_str.o</c:v>
+                </c:pt>
+                <c:pt idx="41">
                   <c:v>rt_memclr_w.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="42">
+                  <c:v>_printf_pad.o</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>sys_stackheap_outer.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="44">
+                  <c:v>lc_numeric_c.o</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>_c16rtomb.o</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>vsnprintf.o</c:v>
+                </c:pt>
+                <c:pt idx="47">
                   <c:v>stm32f4xx_hal_msp.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="48">
+                  <c:v>m_wm.l</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>fpclassify.o</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>_printf_char_common.o</c:v>
+                </c:pt>
+                <c:pt idx="51">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="52">
+                  <c:v>_printf_wchar.o</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>_printf_char.o</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>_printf_charcount.o</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>_printf_truncate.o</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>fz_wm.l</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>libinit2.o</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>_chval.o</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>__scatter_zi.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
-                  <c:v>fz_wm.l</c:v>
-                </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="60">
                   <c:v>fpinit.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="61">
                   <c:v>__scatter_copy.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="62">
                   <c:v>exit.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="63">
+                  <c:v>rt_ctype_table.o</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>_snputc.o</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>__printf_wp.o</c:v>
+                </c:pt>
+                <c:pt idx="66">
                   <c:v>sys_exit.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="67">
                   <c:v>__rtentry2.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="68">
                   <c:v>rtexit2.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="69">
+                  <c:v>_printf_ll.o</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>_printf_l.o</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>rt_locale_intlibspace.o</c:v>
+                </c:pt>
+                <c:pt idx="72">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="73">
                   <c:v>__main.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
-                  <c:v>libinit2.o</c:v>
-                </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="74">
                   <c:v>heapauxi.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="75">
+                  <c:v>_printf_x.o</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>_printf_u.o</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>_printf_s.o</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>_printf_p.o</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>_printf_o.o</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>_printf_n.o</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>_printf_ls.o</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>_printf_llx.o</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>_printf_llu.o</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>_printf_llo.o</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>_printf_lli.o</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>_printf_lld.o</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>_printf_lc.o</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>_printf_i.o</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>_printf_g.o</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>_printf_f.o</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>_printf_e.o</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>_printf_d.o</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>_printf_c.o</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>_printf_a.o</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>__rtentry4.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="96">
+                  <c:v>printf2.o</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>printf1.o</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>_printf_percent_end.o</c:v>
+                </c:pt>
+                <c:pt idx="99">
                   <c:v>stm32f4xx_hal_tim_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="100">
                   <c:v>use_no_semi.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="101">
                   <c:v>rtexit.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="102">
                   <c:v>libshutdown2.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="103">
                   <c:v>libshutdown.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="104">
                   <c:v>libinit.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="105">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -561,146 +933,326 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$48</c:f>
+              <c:f>flash_percent!$B$3:$B$108</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
-                  <c:v>23.37626647949219</c:v>
+                  <c:v>23.55522918701172</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.78063201904297</c:v>
+                  <c:v>9.997054100036621</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.532337188720703</c:v>
+                  <c:v>8.353461265563965</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.231903076171875</c:v>
+                  <c:v>6.238585948944092</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.427371025085449</c:v>
+                  <c:v>5.702503681182861</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.545767784118652</c:v>
+                  <c:v>5.142857074737549</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.380466938018799</c:v>
+                  <c:v>4.076583385467529</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.306012868881226</c:v>
+                  <c:v>3.098674535751343</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.223362445831299</c:v>
+                  <c:v>3.092783451080322</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.223362445831299</c:v>
+                  <c:v>2.362297534942627</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.989186525344849</c:v>
+                  <c:v>2.321060419082642</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.997382760047913</c:v>
+                  <c:v>1.944035291671753</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.804532051086426</c:v>
+                  <c:v>1.625920414924622</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.776981830596924</c:v>
+                  <c:v>1.425625920295715</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.653006434440613</c:v>
+                  <c:v>1.378497838973999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.494593262672424</c:v>
+                  <c:v>1.278350472450256</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.487705707550049</c:v>
+                  <c:v>1.204712867736816</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.336180210113525</c:v>
+                  <c:v>1.107511043548584</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.8816034197807312</c:v>
+                  <c:v>0.9779086709022522</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.8816034197807312</c:v>
+                  <c:v>0.9307805299758911</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.8540533185005188</c:v>
+                  <c:v>0.7746686339378357</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.647427499294281</c:v>
+                  <c:v>0.7717231512069702</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.5372270941734314</c:v>
+                  <c:v>0.7599411010742188</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.509676992893219</c:v>
+                  <c:v>0.7069219350814819</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.3857015073299408</c:v>
+                  <c:v>0.6391752362251282</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.3168262243270874</c:v>
+                  <c:v>0.5832105875015259</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.1928507536649704</c:v>
+                  <c:v>0.5773195624351502</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.179075688123703</c:v>
+                  <c:v>0.5714285969734192</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.179075688123703</c:v>
+                  <c:v>0.553755521774292</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.179075688123703</c:v>
+                  <c:v>0.5243004560470581</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1239754781126976</c:v>
+                  <c:v>0.4064801037311554</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.0826503187417984</c:v>
+                  <c:v>0.3770250380039215</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.0826503187417984</c:v>
+                  <c:v>0.3770250380039215</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.0688752681016922</c:v>
+                  <c:v>0.3770250380039215</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.0551002137362957</c:v>
+                  <c:v>0.3652430176734924</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.0551002137362957</c:v>
+                  <c:v>0.3652430176734924</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.0413251593708992</c:v>
+                  <c:v>0.3652430176734924</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.0413251593708992</c:v>
+                  <c:v>0.353460967540741</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.0413251593708992</c:v>
+                  <c:v>0.3298968970775604</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.02755010686814785</c:v>
+                  <c:v>0.276877760887146</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.01377505343407393</c:v>
+                  <c:v>0.2415316700935364</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.01377505343407393</c:v>
+                  <c:v>0.2297496348619461</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.01377505343407393</c:v>
+                  <c:v>0.2297496348619461</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.01377505343407393</c:v>
+                  <c:v>0.2179675996303558</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.01377505343407393</c:v>
+                  <c:v>0.2120765894651413</c:v>
                 </c:pt>
                 <c:pt idx="45">
+                  <c:v>0.2120765894651413</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.1767304837703705</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.1649484485387802</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.1413843929767609</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.1413843929767609</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.1413843929767609</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.1354933679103851</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.1296023577451706</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.1296023577451706</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.1178203225135803</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.1060382947325707</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.1001472771167755</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.1001472771167755</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.08247422426939011</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.08247422426939011</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.07658321410417557</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.07658321410417557</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.05301914736628532</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.04712812975049019</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.04712812975049019</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.04123711213469505</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.03534609824419022</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.03534609824419022</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.02945508062839508</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.02945508062839508</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.02945508062839508</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.02356406487524509</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.02356406487524509</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.02356406487524509</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.01767304912209511</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.01178203243762255</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.01178203243762255</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.01178203243762255</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.01178203243762255</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.005891016218811274</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.005891016218811274</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.005891016218811274</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.005891016218811274</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.005891016218811274</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -805,8 +1357,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H48" totalsRowCount="1">
-  <autoFilter ref="A2:H47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H108" totalsRowCount="1">
+  <autoFilter ref="A2:H107"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -822,8 +1374,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H48" totalsRowCount="1">
-  <autoFilter ref="A2:H47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H108" totalsRowCount="1">
+  <autoFilter ref="A2:H107"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1123,7 +1675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1136,28 +1688,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="G2" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="H2" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1165,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>41.3681640625</v>
+        <v>37.26346588134766</v>
       </c>
       <c r="C3" s="1">
         <v>1536</v>
@@ -1191,16 +1743,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>27.57877731323242</v>
+        <v>24.86656951904297</v>
       </c>
       <c r="C4" s="1">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D4" s="1">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="E4" s="1">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1209,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1217,16 +1769,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>9.695663452148438</v>
+        <v>11.79039287567139</v>
       </c>
       <c r="C5" s="1">
-        <v>360</v>
+        <v>486</v>
       </c>
       <c r="D5" s="1">
-        <v>660</v>
+        <v>552</v>
       </c>
       <c r="E5" s="1">
-        <v>660</v>
+        <v>552</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1235,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>360</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1243,16 +1795,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>9.049285888671875</v>
+        <v>8.733624458312988</v>
       </c>
       <c r="C6" s="1">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="D6" s="1">
-        <v>480</v>
+        <v>660</v>
       </c>
       <c r="E6" s="1">
-        <v>480</v>
+        <v>660</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1261,7 +1813,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>336</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1269,16 +1821,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>4.847831726074219</v>
+        <v>6.234837532043457</v>
       </c>
       <c r="C7" s="1">
-        <v>180</v>
+        <v>257</v>
       </c>
       <c r="D7" s="1">
-        <v>258</v>
+        <v>2836</v>
       </c>
       <c r="E7" s="1">
-        <v>258</v>
+        <v>2836</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -1287,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>180</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1295,16 +1847,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>2.58551025390625</v>
+        <v>4.366812229156494</v>
       </c>
       <c r="C8" s="1">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="D8" s="1">
-        <v>636</v>
+        <v>258</v>
       </c>
       <c r="E8" s="1">
-        <v>636</v>
+        <v>258</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1313,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>96</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1321,19 +1873,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>2.58551025390625</v>
+        <v>2.328966617584229</v>
       </c>
       <c r="C9" s="1">
         <v>96</v>
       </c>
       <c r="D9" s="1">
-        <v>8</v>
+        <v>7997</v>
       </c>
       <c r="E9" s="1">
-        <v>8</v>
+        <v>7446</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>551</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1347,16 +1899,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>1.939132809638977</v>
+        <v>2.328966617584229</v>
       </c>
       <c r="C10" s="1">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D10" s="1">
-        <v>128</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1">
-        <v>128</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1365,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>72</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1373,25 +1925,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.2423916012048721</v>
+        <v>1.746724843978882</v>
       </c>
       <c r="C11" s="1">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="D11" s="1">
-        <v>217</v>
+        <v>128</v>
       </c>
       <c r="E11" s="1">
-        <v>212</v>
+        <v>128</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>4</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1399,56 +1951,108 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1077295988798142</v>
+        <v>0.2183406054973602</v>
       </c>
       <c r="C12" s="1">
+        <v>9</v>
+      </c>
+      <c r="D12" s="1">
+        <v>217</v>
+      </c>
+      <c r="E12" s="1">
+        <v>212</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>5</v>
+      </c>
+      <c r="H12" s="1">
         <v>4</v>
       </c>
-      <c r="D12" s="1">
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.09704027324914932</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+      <c r="D13" s="1">
         <v>46</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E13" s="1">
         <v>18</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F13" s="1">
         <v>24</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G13" s="1">
         <v>4</v>
       </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" t="s">
-        <v>47</v>
-      </c>
-      <c r="B48">
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.02426006831228733</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1">
+        <v>263</v>
+      </c>
+      <c r="E14" s="1">
+        <v>262</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>107</v>
+      </c>
+      <c r="B108">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C48">
+      <c r="C108">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D48">
+      <c r="D108">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E48">
+      <c r="E108">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F48">
+      <c r="F108">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G48">
+      <c r="G108">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H48">
+      <c r="H108">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1464,7 +2068,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1477,71 +2081,71 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="G2" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="H2" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>23.37626647949219</v>
+        <v>23.55522918701172</v>
       </c>
       <c r="C3" s="1">
-        <v>3394</v>
+        <v>7997</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E3" s="1">
-        <v>3394</v>
+        <v>7446</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>551</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>14.78063201904297</v>
+        <v>9.997054100036621</v>
       </c>
       <c r="C4" s="1">
-        <v>2146</v>
+        <v>3394</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>2146</v>
+        <v>3394</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1555,19 +2159,19 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>9.532337188720703</v>
+        <v>8.353461265563965</v>
       </c>
       <c r="C5" s="1">
-        <v>1384</v>
+        <v>2836</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="E5" s="1">
-        <v>1384</v>
+        <v>2836</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1576,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1584,19 +2188,19 @@
         <v>14</v>
       </c>
       <c r="B6" s="2">
-        <v>7.231903076171875</v>
+        <v>6.238585948944092</v>
       </c>
       <c r="C6" s="1">
-        <v>1050</v>
+        <v>2118</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>1042</v>
+        <v>2118</v>
       </c>
       <c r="F6" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1610,16 +2214,16 @@
         <v>15</v>
       </c>
       <c r="B7" s="2">
-        <v>5.427371025085449</v>
+        <v>5.702503681182861</v>
       </c>
       <c r="C7" s="1">
-        <v>788</v>
+        <v>1936</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>788</v>
+        <v>1936</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -1633,19 +2237,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2">
-        <v>4.545767784118652</v>
+        <v>5.142857074737549</v>
       </c>
       <c r="C8" s="1">
-        <v>660</v>
+        <v>1746</v>
       </c>
       <c r="D8" s="1">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>660</v>
+        <v>1746</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1654,24 +2258,24 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2">
-        <v>4.380466938018799</v>
+        <v>4.076583385467529</v>
       </c>
       <c r="C9" s="1">
-        <v>636</v>
+        <v>1384</v>
       </c>
       <c r="D9" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>636</v>
+        <v>1384</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1680,24 +2284,24 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2">
-        <v>3.306012868881226</v>
+        <v>3.098674535751343</v>
       </c>
       <c r="C10" s="1">
-        <v>480</v>
+        <v>1052</v>
       </c>
       <c r="D10" s="1">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>480</v>
+        <v>1052</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1706,27 +2310,27 @@
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B11" s="2">
-        <v>3.223362445831299</v>
+        <v>3.092783451080322</v>
       </c>
       <c r="C11" s="1">
-        <v>468</v>
+        <v>1050</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>468</v>
+        <v>1042</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1737,45 +2341,45 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2">
-        <v>3.223362445831299</v>
+        <v>2.362297534942627</v>
       </c>
       <c r="C12" s="1">
-        <v>468</v>
+        <v>802</v>
       </c>
       <c r="D12" s="1">
-        <v>1536</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>64</v>
+        <v>764</v>
       </c>
       <c r="F12" s="1">
-        <v>404</v>
+        <v>38</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>1536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2">
-        <v>2.989186525344849</v>
+        <v>2.321060419082642</v>
       </c>
       <c r="C13" s="1">
-        <v>434</v>
+        <v>788</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>434</v>
+        <v>788</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1789,19 +2393,19 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>1.997382760047913</v>
+        <v>1.944035291671753</v>
       </c>
       <c r="C14" s="1">
-        <v>290</v>
+        <v>660</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="E14" s="1">
-        <v>290</v>
+        <v>660</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1810,24 +2414,24 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B15" s="2">
-        <v>1.804532051086426</v>
+        <v>1.625920414924622</v>
       </c>
       <c r="C15" s="1">
-        <v>262</v>
+        <v>552</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>486</v>
       </c>
       <c r="E15" s="1">
-        <v>262</v>
+        <v>552</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -1836,24 +2440,24 @@
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>486</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2">
-        <v>1.776981830596924</v>
+        <v>1.425625920295715</v>
       </c>
       <c r="C16" s="1">
-        <v>258</v>
+        <v>484</v>
       </c>
       <c r="D16" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>258</v>
+        <v>484</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1862,105 +2466,105 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>1.653006434440613</v>
+        <v>1.378497838973999</v>
       </c>
       <c r="C17" s="1">
-        <v>240</v>
+        <v>468</v>
       </c>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>1536</v>
       </c>
       <c r="E17" s="1">
-        <v>240</v>
+        <v>64</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B18" s="2">
-        <v>1.494593262672424</v>
+        <v>1.278350472450256</v>
       </c>
       <c r="C18" s="1">
-        <v>217</v>
+        <v>434</v>
       </c>
       <c r="D18" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>212</v>
+        <v>434</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B19" s="2">
-        <v>1.487705707550049</v>
+        <v>1.204712867736816</v>
       </c>
       <c r="C19" s="1">
-        <v>216</v>
+        <v>409</v>
       </c>
       <c r="D19" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>216</v>
+        <v>392</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2">
-        <v>1.336180210113525</v>
+        <v>1.107511043548584</v>
       </c>
       <c r="C20" s="1">
-        <v>194</v>
+        <v>376</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -1971,19 +2575,19 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B21" s="2">
-        <v>0.8816034197807312</v>
+        <v>0.9779086709022522</v>
       </c>
       <c r="C21" s="1">
-        <v>128</v>
+        <v>332</v>
       </c>
       <c r="D21" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>128</v>
+        <v>332</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1992,27 +2596,27 @@
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B22" s="2">
-        <v>0.8816034197807312</v>
+        <v>0.9307805299758911</v>
       </c>
       <c r="C22" s="1">
-        <v>128</v>
+        <v>316</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="F22" s="1">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
@@ -2023,25 +2627,25 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B23" s="2">
-        <v>0.8540533185005188</v>
+        <v>0.7746686339378357</v>
       </c>
       <c r="C23" s="1">
-        <v>124</v>
+        <v>263</v>
       </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="1">
-        <v>124</v>
+        <v>262</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
@@ -2049,19 +2653,19 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B24" s="2">
-        <v>0.647427499294281</v>
+        <v>0.7717231512069702</v>
       </c>
       <c r="C24" s="1">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2075,19 +2679,19 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B25" s="2">
-        <v>0.5372270941734314</v>
+        <v>0.7599411010742188</v>
       </c>
       <c r="C25" s="1">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E25" s="1">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2096,24 +2700,24 @@
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B26" s="2">
-        <v>0.509676992893219</v>
+        <v>0.7069219350814819</v>
       </c>
       <c r="C26" s="1">
-        <v>74</v>
+        <v>240</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>74</v>
+        <v>240</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2127,74 +2731,74 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B27" s="2">
-        <v>0.3857015073299408</v>
+        <v>0.6391752362251282</v>
       </c>
       <c r="C27" s="1">
-        <v>56</v>
+        <v>217</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E27" s="1">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B28" s="2">
-        <v>0.3168262243270874</v>
+        <v>0.5832105875015259</v>
       </c>
       <c r="C28" s="1">
-        <v>46</v>
+        <v>198</v>
       </c>
       <c r="D28" s="1">
-        <v>4</v>
+        <v>1025</v>
       </c>
       <c r="E28" s="1">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="F28" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B29" s="2">
-        <v>0.1928507536649704</v>
+        <v>0.5773195624351502</v>
       </c>
       <c r="C29" s="1">
-        <v>28</v>
+        <v>196</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="F29" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
@@ -2205,19 +2809,19 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B30" s="2">
-        <v>0.179075688123703</v>
+        <v>0.5714285969734192</v>
       </c>
       <c r="C30" s="1">
-        <v>26</v>
+        <v>194</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>26</v>
+        <v>194</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2231,22 +2835,22 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B31" s="2">
-        <v>0.179075688123703</v>
+        <v>0.553755521774292</v>
       </c>
       <c r="C31" s="1">
-        <v>26</v>
+        <v>188</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>26</v>
+        <v>148</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -2257,19 +2861,19 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B32" s="2">
-        <v>0.179075688123703</v>
+        <v>0.5243004560470581</v>
       </c>
       <c r="C32" s="1">
-        <v>26</v>
+        <v>178</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>26</v>
+        <v>178</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2283,19 +2887,19 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1239754781126976</v>
+        <v>0.4064801037311554</v>
       </c>
       <c r="C33" s="1">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2309,19 +2913,19 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B34" s="2">
-        <v>0.0826503187417984</v>
+        <v>0.3770250380039215</v>
       </c>
       <c r="C34" s="1">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2335,19 +2939,19 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B35" s="2">
-        <v>0.0826503187417984</v>
+        <v>0.3770250380039215</v>
       </c>
       <c r="C35" s="1">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="D35" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E35" s="1">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2356,24 +2960,24 @@
         <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" s="2">
-        <v>0.0688752681016922</v>
+        <v>0.3770250380039215</v>
       </c>
       <c r="C36" s="1">
-        <v>10</v>
+        <v>128</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>10</v>
+        <v>128</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2387,19 +2991,19 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2">
-        <v>0.0551002137362957</v>
+        <v>0.3652430176734924</v>
       </c>
       <c r="C37" s="1">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="D37" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2408,24 +3012,24 @@
         <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B38" s="2">
-        <v>0.0551002137362957</v>
+        <v>0.3652430176734924</v>
       </c>
       <c r="C38" s="1">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2439,19 +3043,19 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2">
-        <v>0.0413251593708992</v>
+        <v>0.3652430176734924</v>
       </c>
       <c r="C39" s="1">
-        <v>6</v>
+        <v>124</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>6</v>
+        <v>124</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2465,19 +3069,19 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B40" s="2">
-        <v>0.0413251593708992</v>
+        <v>0.353460967540741</v>
       </c>
       <c r="C40" s="1">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -2491,19 +3095,19 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>0.0413251593708992</v>
+        <v>0.3298968970775604</v>
       </c>
       <c r="C41" s="1">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -2517,19 +3121,19 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2">
-        <v>0.02755010686814785</v>
+        <v>0.276877760887146</v>
       </c>
       <c r="C42" s="1">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -2543,19 +3147,19 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B43" s="2">
-        <v>0.01377505343407393</v>
+        <v>0.2415316700935364</v>
       </c>
       <c r="C43" s="1">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -2569,19 +3173,19 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B44" s="2">
-        <v>0.01377505343407393</v>
+        <v>0.2297496348619461</v>
       </c>
       <c r="C44" s="1">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -2595,19 +3199,19 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B45" s="2">
-        <v>0.01377505343407393</v>
+        <v>0.2297496348619461</v>
       </c>
       <c r="C45" s="1">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -2621,19 +3225,19 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B46" s="2">
-        <v>0.01377505343407393</v>
+        <v>0.2179675996303558</v>
       </c>
       <c r="C46" s="1">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -2647,59 +3251,1619 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B47" s="2">
-        <v>0.01377505343407393</v>
+        <v>0.2120765894651413</v>
       </c>
       <c r="C47" s="1">
+        <v>72</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
+      <c r="E47" s="1">
+        <v>44</v>
+      </c>
+      <c r="F47" s="1">
+        <v>28</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="2">
+        <v>0.2120765894651413</v>
+      </c>
+      <c r="C48" s="1">
+        <v>72</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
+      <c r="E48" s="1">
+        <v>72</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0.1767304837703705</v>
+      </c>
+      <c r="C49" s="1">
+        <v>60</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0</v>
+      </c>
+      <c r="E49" s="1">
+        <v>60</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" s="2">
+        <v>0.1649484485387802</v>
+      </c>
+      <c r="C50" s="1">
+        <v>56</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0</v>
+      </c>
+      <c r="E50" s="1">
+        <v>56</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" s="2">
+        <v>0.1413843929767609</v>
+      </c>
+      <c r="C51" s="1">
+        <v>48</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0</v>
+      </c>
+      <c r="E51" s="1">
+        <v>48</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" s="2">
+        <v>0.1413843929767609</v>
+      </c>
+      <c r="C52" s="1">
+        <v>48</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0</v>
+      </c>
+      <c r="E52" s="1">
+        <v>48</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="2">
+        <v>0.1413843929767609</v>
+      </c>
+      <c r="C53" s="1">
+        <v>48</v>
+      </c>
+      <c r="D53" s="1">
+        <v>0</v>
+      </c>
+      <c r="E53" s="1">
+        <v>48</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" s="2">
+        <v>0.1354933679103851</v>
+      </c>
+      <c r="C54" s="1">
+        <v>46</v>
+      </c>
+      <c r="D54" s="1">
+        <v>4</v>
+      </c>
+      <c r="E54" s="1">
+        <v>18</v>
+      </c>
+      <c r="F54" s="1">
+        <v>24</v>
+      </c>
+      <c r="G54" s="1">
+        <v>4</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2">
+        <v>0.1296023577451706</v>
+      </c>
+      <c r="C55" s="1">
+        <v>44</v>
+      </c>
+      <c r="D55" s="1">
+        <v>0</v>
+      </c>
+      <c r="E55" s="1">
+        <v>44</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2">
+        <v>0.1296023577451706</v>
+      </c>
+      <c r="C56" s="1">
+        <v>44</v>
+      </c>
+      <c r="D56" s="1">
+        <v>0</v>
+      </c>
+      <c r="E56" s="1">
+        <v>44</v>
+      </c>
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2">
+        <v>0.1178203225135803</v>
+      </c>
+      <c r="C57" s="1">
+        <v>40</v>
+      </c>
+      <c r="D57" s="1">
+        <v>0</v>
+      </c>
+      <c r="E57" s="1">
+        <v>40</v>
+      </c>
+      <c r="F57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2">
+        <v>0.1060382947325707</v>
+      </c>
+      <c r="C58" s="1">
+        <v>36</v>
+      </c>
+      <c r="D58" s="1">
+        <v>0</v>
+      </c>
+      <c r="E58" s="1">
+        <v>36</v>
+      </c>
+      <c r="F58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2">
+        <v>0.1001472771167755</v>
+      </c>
+      <c r="C59" s="1">
+        <v>34</v>
+      </c>
+      <c r="D59" s="1">
+        <v>0</v>
+      </c>
+      <c r="E59" s="1">
+        <v>34</v>
+      </c>
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2">
+        <v>0.1001472771167755</v>
+      </c>
+      <c r="C60" s="1">
+        <v>34</v>
+      </c>
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
+        <v>34</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2">
+        <v>0.08247422426939011</v>
+      </c>
+      <c r="C61" s="1">
+        <v>28</v>
+      </c>
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+      <c r="E61" s="1">
+        <v>28</v>
+      </c>
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2">
+        <v>0.08247422426939011</v>
+      </c>
+      <c r="C62" s="1">
+        <v>28</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0</v>
+      </c>
+      <c r="E62" s="1">
+        <v>28</v>
+      </c>
+      <c r="F62" s="1">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2">
+        <v>0.07658321410417557</v>
+      </c>
+      <c r="C63" s="1">
+        <v>26</v>
+      </c>
+      <c r="D63" s="1">
+        <v>0</v>
+      </c>
+      <c r="E63" s="1">
+        <v>26</v>
+      </c>
+      <c r="F63" s="1">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2">
+        <v>0.07658321410417557</v>
+      </c>
+      <c r="C64" s="1">
+        <v>26</v>
+      </c>
+      <c r="D64" s="1">
+        <v>0</v>
+      </c>
+      <c r="E64" s="1">
+        <v>26</v>
+      </c>
+      <c r="F64" s="1">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2">
+        <v>0.05301914736628532</v>
+      </c>
+      <c r="C65" s="1">
+        <v>18</v>
+      </c>
+      <c r="D65" s="1">
+        <v>0</v>
+      </c>
+      <c r="E65" s="1">
+        <v>18</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2">
+        <v>0.04712812975049019</v>
+      </c>
+      <c r="C66" s="1">
+        <v>16</v>
+      </c>
+      <c r="D66" s="1">
+        <v>0</v>
+      </c>
+      <c r="E66" s="1">
+        <v>16</v>
+      </c>
+      <c r="F66" s="1">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2">
+        <v>0.04712812975049019</v>
+      </c>
+      <c r="C67" s="1">
+        <v>16</v>
+      </c>
+      <c r="D67" s="1">
+        <v>0</v>
+      </c>
+      <c r="E67" s="1">
+        <v>16</v>
+      </c>
+      <c r="F67" s="1">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2">
+        <v>0.04123711213469505</v>
+      </c>
+      <c r="C68" s="1">
+        <v>14</v>
+      </c>
+      <c r="D68" s="1">
+        <v>0</v>
+      </c>
+      <c r="E68" s="1">
+        <v>14</v>
+      </c>
+      <c r="F68" s="1">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2">
+        <v>0.03534609824419022</v>
+      </c>
+      <c r="C69" s="1">
+        <v>12</v>
+      </c>
+      <c r="D69" s="1">
+        <v>0</v>
+      </c>
+      <c r="E69" s="1">
+        <v>12</v>
+      </c>
+      <c r="F69" s="1">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2">
+        <v>0.03534609824419022</v>
+      </c>
+      <c r="C70" s="1">
+        <v>12</v>
+      </c>
+      <c r="D70" s="1">
+        <v>0</v>
+      </c>
+      <c r="E70" s="1">
+        <v>12</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2">
+        <v>0.02945508062839508</v>
+      </c>
+      <c r="C71" s="1">
+        <v>10</v>
+      </c>
+      <c r="D71" s="1">
+        <v>0</v>
+      </c>
+      <c r="E71" s="1">
+        <v>10</v>
+      </c>
+      <c r="F71" s="1">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2">
+        <v>0.02945508062839508</v>
+      </c>
+      <c r="C72" s="1">
+        <v>10</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1">
+        <v>10</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2">
+        <v>0.02945508062839508</v>
+      </c>
+      <c r="C73" s="1">
+        <v>10</v>
+      </c>
+      <c r="D73" s="1">
+        <v>0</v>
+      </c>
+      <c r="E73" s="1">
+        <v>10</v>
+      </c>
+      <c r="F73" s="1">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2">
+        <v>0.02356406487524509</v>
+      </c>
+      <c r="C74" s="1">
+        <v>8</v>
+      </c>
+      <c r="D74" s="1">
+        <v>0</v>
+      </c>
+      <c r="E74" s="1">
+        <v>8</v>
+      </c>
+      <c r="F74" s="1">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B75" s="2">
+        <v>0.02356406487524509</v>
+      </c>
+      <c r="C75" s="1">
+        <v>8</v>
+      </c>
+      <c r="D75" s="1">
+        <v>96</v>
+      </c>
+      <c r="E75" s="1">
+        <v>8</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B76" s="2">
+        <v>0.02356406487524509</v>
+      </c>
+      <c r="C76" s="1">
+        <v>8</v>
+      </c>
+      <c r="D76" s="1">
+        <v>0</v>
+      </c>
+      <c r="E76" s="1">
+        <v>8</v>
+      </c>
+      <c r="F76" s="1">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B77" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C77" s="1">
+        <v>6</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0</v>
+      </c>
+      <c r="E77" s="1">
+        <v>6</v>
+      </c>
+      <c r="F77" s="1">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B78" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C78" s="1">
+        <v>6</v>
+      </c>
+      <c r="D78" s="1">
+        <v>0</v>
+      </c>
+      <c r="E78" s="1">
+        <v>6</v>
+      </c>
+      <c r="F78" s="1">
+        <v>0</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0</v>
+      </c>
+      <c r="H78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C79" s="1">
+        <v>6</v>
+      </c>
+      <c r="D79" s="1">
+        <v>0</v>
+      </c>
+      <c r="E79" s="1">
+        <v>6</v>
+      </c>
+      <c r="F79" s="1">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0</v>
+      </c>
+      <c r="H79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B80" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C80" s="1">
+        <v>6</v>
+      </c>
+      <c r="D80" s="1">
+        <v>0</v>
+      </c>
+      <c r="E80" s="1">
+        <v>6</v>
+      </c>
+      <c r="F80" s="1">
+        <v>0</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B81" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C81" s="1">
+        <v>6</v>
+      </c>
+      <c r="D81" s="1">
+        <v>0</v>
+      </c>
+      <c r="E81" s="1">
+        <v>6</v>
+      </c>
+      <c r="F81" s="1">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B82" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C82" s="1">
+        <v>6</v>
+      </c>
+      <c r="D82" s="1">
+        <v>0</v>
+      </c>
+      <c r="E82" s="1">
+        <v>6</v>
+      </c>
+      <c r="F82" s="1">
+        <v>0</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+      <c r="H82" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B83" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C83" s="1">
+        <v>6</v>
+      </c>
+      <c r="D83" s="1">
+        <v>0</v>
+      </c>
+      <c r="E83" s="1">
+        <v>6</v>
+      </c>
+      <c r="F83" s="1">
+        <v>0</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0</v>
+      </c>
+      <c r="H83" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B84" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C84" s="1">
+        <v>6</v>
+      </c>
+      <c r="D84" s="1">
+        <v>0</v>
+      </c>
+      <c r="E84" s="1">
+        <v>6</v>
+      </c>
+      <c r="F84" s="1">
+        <v>0</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B85" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C85" s="1">
+        <v>6</v>
+      </c>
+      <c r="D85" s="1">
+        <v>0</v>
+      </c>
+      <c r="E85" s="1">
+        <v>6</v>
+      </c>
+      <c r="F85" s="1">
+        <v>0</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0</v>
+      </c>
+      <c r="H85" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B86" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C86" s="1">
+        <v>6</v>
+      </c>
+      <c r="D86" s="1">
+        <v>0</v>
+      </c>
+      <c r="E86" s="1">
+        <v>6</v>
+      </c>
+      <c r="F86" s="1">
+        <v>0</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0</v>
+      </c>
+      <c r="H86" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B87" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C87" s="1">
+        <v>6</v>
+      </c>
+      <c r="D87" s="1">
+        <v>0</v>
+      </c>
+      <c r="E87" s="1">
+        <v>6</v>
+      </c>
+      <c r="F87" s="1">
+        <v>0</v>
+      </c>
+      <c r="G87" s="1">
+        <v>0</v>
+      </c>
+      <c r="H87" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B88" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C88" s="1">
+        <v>6</v>
+      </c>
+      <c r="D88" s="1">
+        <v>0</v>
+      </c>
+      <c r="E88" s="1">
+        <v>6</v>
+      </c>
+      <c r="F88" s="1">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+      <c r="H88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B89" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C89" s="1">
+        <v>6</v>
+      </c>
+      <c r="D89" s="1">
+        <v>0</v>
+      </c>
+      <c r="E89" s="1">
+        <v>6</v>
+      </c>
+      <c r="F89" s="1">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+      <c r="H89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B90" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C90" s="1">
+        <v>6</v>
+      </c>
+      <c r="D90" s="1">
+        <v>0</v>
+      </c>
+      <c r="E90" s="1">
+        <v>6</v>
+      </c>
+      <c r="F90" s="1">
+        <v>0</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+      <c r="H90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B91" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C91" s="1">
+        <v>6</v>
+      </c>
+      <c r="D91" s="1">
+        <v>0</v>
+      </c>
+      <c r="E91" s="1">
+        <v>6</v>
+      </c>
+      <c r="F91" s="1">
+        <v>0</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0</v>
+      </c>
+      <c r="H91" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B92" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C92" s="1">
+        <v>6</v>
+      </c>
+      <c r="D92" s="1">
+        <v>0</v>
+      </c>
+      <c r="E92" s="1">
+        <v>6</v>
+      </c>
+      <c r="F92" s="1">
+        <v>0</v>
+      </c>
+      <c r="G92" s="1">
+        <v>0</v>
+      </c>
+      <c r="H92" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B93" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C93" s="1">
+        <v>6</v>
+      </c>
+      <c r="D93" s="1">
+        <v>0</v>
+      </c>
+      <c r="E93" s="1">
+        <v>6</v>
+      </c>
+      <c r="F93" s="1">
+        <v>0</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0</v>
+      </c>
+      <c r="H93" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B94" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C94" s="1">
+        <v>6</v>
+      </c>
+      <c r="D94" s="1">
+        <v>0</v>
+      </c>
+      <c r="E94" s="1">
+        <v>6</v>
+      </c>
+      <c r="F94" s="1">
+        <v>0</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0</v>
+      </c>
+      <c r="H94" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B95" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C95" s="1">
+        <v>6</v>
+      </c>
+      <c r="D95" s="1">
+        <v>0</v>
+      </c>
+      <c r="E95" s="1">
+        <v>6</v>
+      </c>
+      <c r="F95" s="1">
+        <v>0</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0</v>
+      </c>
+      <c r="H95" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B96" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C96" s="1">
+        <v>6</v>
+      </c>
+      <c r="D96" s="1">
+        <v>0</v>
+      </c>
+      <c r="E96" s="1">
+        <v>6</v>
+      </c>
+      <c r="F96" s="1">
+        <v>0</v>
+      </c>
+      <c r="G96" s="1">
+        <v>0</v>
+      </c>
+      <c r="H96" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B97" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C97" s="1">
+        <v>6</v>
+      </c>
+      <c r="D97" s="1">
+        <v>0</v>
+      </c>
+      <c r="E97" s="1">
+        <v>6</v>
+      </c>
+      <c r="F97" s="1">
+        <v>0</v>
+      </c>
+      <c r="G97" s="1">
+        <v>0</v>
+      </c>
+      <c r="H97" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B98" s="2">
+        <v>0.01767304912209511</v>
+      </c>
+      <c r="C98" s="1">
+        <v>6</v>
+      </c>
+      <c r="D98" s="1">
+        <v>0</v>
+      </c>
+      <c r="E98" s="1">
+        <v>6</v>
+      </c>
+      <c r="F98" s="1">
+        <v>0</v>
+      </c>
+      <c r="G98" s="1">
+        <v>0</v>
+      </c>
+      <c r="H98" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B99" s="2">
+        <v>0.01178203243762255</v>
+      </c>
+      <c r="C99" s="1">
+        <v>4</v>
+      </c>
+      <c r="D99" s="1">
+        <v>0</v>
+      </c>
+      <c r="E99" s="1">
+        <v>4</v>
+      </c>
+      <c r="F99" s="1">
+        <v>0</v>
+      </c>
+      <c r="G99" s="1">
+        <v>0</v>
+      </c>
+      <c r="H99" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B100" s="2">
+        <v>0.01178203243762255</v>
+      </c>
+      <c r="C100" s="1">
+        <v>4</v>
+      </c>
+      <c r="D100" s="1">
+        <v>0</v>
+      </c>
+      <c r="E100" s="1">
+        <v>4</v>
+      </c>
+      <c r="F100" s="1">
+        <v>0</v>
+      </c>
+      <c r="G100" s="1">
+        <v>0</v>
+      </c>
+      <c r="H100" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B101" s="2">
+        <v>0.01178203243762255</v>
+      </c>
+      <c r="C101" s="1">
+        <v>4</v>
+      </c>
+      <c r="D101" s="1">
+        <v>0</v>
+      </c>
+      <c r="E101" s="1">
+        <v>4</v>
+      </c>
+      <c r="F101" s="1">
+        <v>0</v>
+      </c>
+      <c r="G101" s="1">
+        <v>0</v>
+      </c>
+      <c r="H101" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B102" s="2">
+        <v>0.01178203243762255</v>
+      </c>
+      <c r="C102" s="1">
+        <v>4</v>
+      </c>
+      <c r="D102" s="1">
+        <v>0</v>
+      </c>
+      <c r="E102" s="1">
+        <v>4</v>
+      </c>
+      <c r="F102" s="1">
+        <v>0</v>
+      </c>
+      <c r="G102" s="1">
+        <v>0</v>
+      </c>
+      <c r="H102" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B103" s="2">
+        <v>0.005891016218811274</v>
+      </c>
+      <c r="C103" s="1">
         <v>2</v>
       </c>
-      <c r="D47" s="1">
-        <v>0</v>
-      </c>
-      <c r="E47" s="1">
+      <c r="D103" s="1">
+        <v>0</v>
+      </c>
+      <c r="E103" s="1">
         <v>2</v>
       </c>
-      <c r="F47" s="1">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0</v>
-      </c>
-      <c r="H47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" t="s">
-        <v>47</v>
-      </c>
-      <c r="B48">
+      <c r="F103" s="1">
+        <v>0</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0</v>
+      </c>
+      <c r="H103" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B104" s="2">
+        <v>0.005891016218811274</v>
+      </c>
+      <c r="C104" s="1">
+        <v>2</v>
+      </c>
+      <c r="D104" s="1">
+        <v>0</v>
+      </c>
+      <c r="E104" s="1">
+        <v>2</v>
+      </c>
+      <c r="F104" s="1">
+        <v>0</v>
+      </c>
+      <c r="G104" s="1">
+        <v>0</v>
+      </c>
+      <c r="H104" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B105" s="2">
+        <v>0.005891016218811274</v>
+      </c>
+      <c r="C105" s="1">
+        <v>2</v>
+      </c>
+      <c r="D105" s="1">
+        <v>0</v>
+      </c>
+      <c r="E105" s="1">
+        <v>2</v>
+      </c>
+      <c r="F105" s="1">
+        <v>0</v>
+      </c>
+      <c r="G105" s="1">
+        <v>0</v>
+      </c>
+      <c r="H105" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B106" s="2">
+        <v>0.005891016218811274</v>
+      </c>
+      <c r="C106" s="1">
+        <v>2</v>
+      </c>
+      <c r="D106" s="1">
+        <v>0</v>
+      </c>
+      <c r="E106" s="1">
+        <v>2</v>
+      </c>
+      <c r="F106" s="1">
+        <v>0</v>
+      </c>
+      <c r="G106" s="1">
+        <v>0</v>
+      </c>
+      <c r="H106" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B107" s="2">
+        <v>0.005891016218811274</v>
+      </c>
+      <c r="C107" s="1">
+        <v>2</v>
+      </c>
+      <c r="D107" s="1">
+        <v>0</v>
+      </c>
+      <c r="E107" s="1">
+        <v>2</v>
+      </c>
+      <c r="F107" s="1">
+        <v>0</v>
+      </c>
+      <c r="G107" s="1">
+        <v>0</v>
+      </c>
+      <c r="H107" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>107</v>
+      </c>
+      <c r="B108">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C48">
+      <c r="C108">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D48">
+      <c r="D108">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E48">
+      <c r="E108">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F48">
+      <c r="F108">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G48">
+      <c r="G108">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H48">
+      <c r="H108">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/MDK-ARM/F401RC_analysis.xlsx
+++ b/MDK-ARM/F401RC_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="116">
   <si>
     <t>F401RC</t>
   </si>
@@ -26,12 +26,12 @@
     <t>usart_idel_config.o</t>
   </si>
   <si>
+    <t>spi.o</t>
+  </si>
+  <si>
     <t>usart.o</t>
   </si>
   <si>
-    <t>spi.o</t>
-  </si>
-  <si>
     <t>st7789.o</t>
   </si>
   <si>
@@ -53,7 +53,10 @@
     <t>system_stm32f4xx.o</t>
   </si>
   <si>
-    <t>w25qxx.o</t>
+    <t>multi_button.o</t>
+  </si>
+  <si>
+    <t>stm32f4xx_it.o</t>
   </si>
   <si>
     <t>stm32f4xx_hal_i2c.o</t>
@@ -65,12 +68,12 @@
     <t>btod.o</t>
   </si>
   <si>
+    <t>stm32f4xx_hal_rcc.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal_spi.o</t>
   </si>
   <si>
-    <t>stm32f4xx_hal_rcc.o</t>
-  </si>
-  <si>
     <t>_printf_fp_dec.o</t>
   </si>
   <si>
@@ -83,24 +86,24 @@
     <t>stm32f4xx_hal_tim.o</t>
   </si>
   <si>
+    <t>stm32f4xx_hal_gpio.o</t>
+  </si>
+  <si>
+    <t>__printf_flags_ss_wp.o</t>
+  </si>
+  <si>
+    <t>bigflt0.o</t>
+  </si>
+  <si>
+    <t>_scanf_int.o</t>
+  </si>
+  <si>
+    <t>lc_ctype_c.o</t>
+  </si>
+  <si>
     <t>main.o</t>
   </si>
   <si>
-    <t>stm32f4xx_hal_gpio.o</t>
-  </si>
-  <si>
-    <t>__printf_flags_ss_wp.o</t>
-  </si>
-  <si>
-    <t>bigflt0.o</t>
-  </si>
-  <si>
-    <t>_scanf_int.o</t>
-  </si>
-  <si>
-    <t>lc_ctype_c.o</t>
-  </si>
-  <si>
     <t>gpio.o</t>
   </si>
   <si>
@@ -119,22 +122,19 @@
     <t>_printf_intcommon.o</t>
   </si>
   <si>
+    <t>dma.o</t>
+  </si>
+  <si>
     <t>lludiv10.o</t>
   </si>
   <si>
     <t>_printf_fp_infnan.o</t>
   </si>
   <si>
-    <t>stm32f4xx_it.o</t>
-  </si>
-  <si>
     <t>strcmpv7em.o</t>
   </si>
   <si>
     <t>_printf_longlong_dec.o</t>
-  </si>
-  <si>
-    <t>dma.o</t>
   </si>
   <si>
     <t>_printf_dec.o</t>
@@ -462,10 +462,10 @@
                   <c:v>usart_idel_config.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>spi.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>usart.o</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>spi.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>st7789.o</c:v>
@@ -489,7 +489,10 @@
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>w25qxx.o</c:v>
+                  <c:v>multi_button.o</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>Totals</c:v>
@@ -504,40 +507,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="106"/>
                 <c:pt idx="0">
-                  <c:v>37.26346588134766</c:v>
+                  <c:v>35.57202529907227</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24.86656951904297</c:v>
+                  <c:v>23.73784065246582</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.79039287567139</c:v>
+                  <c:v>12.78369617462158</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.733624458312988</c:v>
+                  <c:v>11.25521087646484</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.234837532043457</c:v>
+                  <c:v>5.951829433441162</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.366812229156494</c:v>
+                  <c:v>4.168596744537354</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.328966617584229</c:v>
+                  <c:v>2.223251581192017</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.328966617584229</c:v>
+                  <c:v>2.223251581192017</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.746724843978882</c:v>
+                  <c:v>1.667438626289368</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2183406054973602</c:v>
+                  <c:v>0.208429828286171</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.09704027324914932</c:v>
+                  <c:v>0.09263548254966736</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.02426006831228733</c:v>
+                  <c:v>0.09263548254966736</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.02315887063741684</c:v>
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>0</c:v>
@@ -626,10 +632,10 @@
                   <c:v>btod.o</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>stm32f4xx_hal_rcc.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>stm32f4xx_hal_spi.o</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>stm32f4xx_hal_rcc.o</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>_printf_fp_dec.o</c:v>
@@ -650,10 +656,10 @@
                   <c:v>usart.o</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>main.o</c:v>
+                  <c:v>startup_stm32f401xc.o</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>startup_stm32f401xc.o</c:v>
+                  <c:v>multi_button.o</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>stm32f4xx_hal_gpio.o</c:v>
@@ -671,7 +677,7 @@
                   <c:v>lc_ctype_c.o</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>w25qxx.o</c:v>
+                  <c:v>main.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>gpio.o</c:v>
@@ -689,37 +695,37 @@
                   <c:v>usart_idel_config.o</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>stm32f4xx_it.o</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>_printf_wctomb.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>stm32f4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>_printf_hex_int_ll_ptr.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>_printf_intcommon.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
+                  <c:v>dma.o</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>lludiv10.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="33">
                   <c:v>_printf_fp_infnan.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="34">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
-                  <c:v>stm32f4xx_it.o</c:v>
-                </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="35">
                   <c:v>strcmpv7em.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="36">
                   <c:v>_printf_longlong_dec.o</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>dma.o</c:v>
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>_printf_dec.o</c:v>
@@ -938,319 +944,319 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="106"/>
                 <c:pt idx="0">
-                  <c:v>23.55522918701172</c:v>
+                  <c:v>23.87948226928711</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.997054100036621</c:v>
+                  <c:v>10.13467121124268</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.353461265563965</c:v>
+                  <c:v>8.1220703125</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.238585948944092</c:v>
+                  <c:v>6.324464797973633</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.702503681182861</c:v>
+                  <c:v>5.781002521514893</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.142857074737549</c:v>
+                  <c:v>4.132700443267822</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.076583385467529</c:v>
+                  <c:v>3.427991390228272</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.098674535751343</c:v>
+                  <c:v>3.141330003738403</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.092783451080322</c:v>
+                  <c:v>3.135357856750488</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.362297534942627</c:v>
+                  <c:v>2.394816160202026</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.321060419082642</c:v>
+                  <c:v>2.3530113697052</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.944035291671753</c:v>
+                  <c:v>2.3530113697052</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.625920414924622</c:v>
+                  <c:v>1.648302435874939</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.425625920295715</c:v>
+                  <c:v>1.397473812103272</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.378497838973999</c:v>
+                  <c:v>1.379557490348816</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.278350472450256</c:v>
+                  <c:v>1.295947909355164</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.204712867736816</c:v>
+                  <c:v>1.221296548843384</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.107511043548584</c:v>
+                  <c:v>1.122756719589233</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.9779086709022522</c:v>
+                  <c:v>0.9913703203201294</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.9307805299758911</c:v>
+                  <c:v>0.943593442440033</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.7746686339378357</c:v>
+                  <c:v>0.9197049736976624</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.7717231512069702</c:v>
+                  <c:v>0.7823464274406433</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.7599411010742188</c:v>
+                  <c:v>0.770402193069458</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.7069219350814819</c:v>
+                  <c:v>0.7166532278060913</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6391752362251282</c:v>
+                  <c:v>0.6479739546775818</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.5832105875015259</c:v>
+                  <c:v>0.5912389159202576</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.5773195624351502</c:v>
+                  <c:v>0.5912389159202576</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.5714285969734192</c:v>
+                  <c:v>0.5852668285369873</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.553755521774292</c:v>
+                  <c:v>0.5792946815490723</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.5243004560470581</c:v>
+                  <c:v>0.5613783597946167</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.4064801037311554</c:v>
+                  <c:v>0.5315178036689758</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.3770250380039215</c:v>
+                  <c:v>0.4658246040344238</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.3770250380039215</c:v>
+                  <c:v>0.4120756089687347</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.3770250380039215</c:v>
+                  <c:v>0.3822150528430939</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.3652430176734924</c:v>
+                  <c:v>0.3822150528430939</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.3652430176734924</c:v>
+                  <c:v>0.370270848274231</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.3652430176734924</c:v>
+                  <c:v>0.370270848274231</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.353460967540741</c:v>
+                  <c:v>0.3583266139030457</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.3298968970775604</c:v>
+                  <c:v>0.3344381749629974</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.276877760887146</c:v>
+                  <c:v>0.2806891798973084</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.2415316700935364</c:v>
+                  <c:v>0.244856521487236</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.2297496348619461</c:v>
+                  <c:v>0.2329123020172119</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.2297496348619461</c:v>
+                  <c:v>0.2329123020172119</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2179675996303558</c:v>
+                  <c:v>0.2209680825471878</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2120765894651413</c:v>
+                  <c:v>0.2149959653615952</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2120765894651413</c:v>
+                  <c:v>0.2149959653615952</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.1767304837703705</c:v>
+                  <c:v>0.1791633069515228</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.1649484485387802</c:v>
+                  <c:v>0.1672190874814987</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.1413843929767609</c:v>
+                  <c:v>0.1433306485414505</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.1413843929767609</c:v>
+                  <c:v>0.1433306485414505</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.1413843929767609</c:v>
+                  <c:v>0.1433306485414505</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.1354933679103851</c:v>
+                  <c:v>0.1373585313558579</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.1296023577451706</c:v>
+                  <c:v>0.1313864290714264</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.1296023577451706</c:v>
+                  <c:v>0.1313864290714264</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1178203225135803</c:v>
+                  <c:v>0.1194422021508217</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.1060382947325707</c:v>
+                  <c:v>0.1074979826807976</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1001472771167755</c:v>
+                  <c:v>0.1015258729457855</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.1001472771167755</c:v>
+                  <c:v>0.1015258729457855</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.08247422426939011</c:v>
+                  <c:v>0.08360954374074936</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.08247422426939011</c:v>
+                  <c:v>0.08360954374074936</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.07658321410417557</c:v>
+                  <c:v>0.07763743400573731</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.07658321410417557</c:v>
+                  <c:v>0.07763743400573731</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.05301914736628532</c:v>
+                  <c:v>0.05374899134039879</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.04712812975049019</c:v>
+                  <c:v>0.04777688160538673</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.04712812975049019</c:v>
+                  <c:v>0.04777688160538673</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.04123711213469505</c:v>
+                  <c:v>0.04180477187037468</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.03534609824419022</c:v>
+                  <c:v>0.03583266213536263</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.03534609824419022</c:v>
+                  <c:v>0.03583266213536263</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.02945508062839508</c:v>
+                  <c:v>0.02986055053770542</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.02945508062839508</c:v>
+                  <c:v>0.02986055053770542</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.02945508062839508</c:v>
+                  <c:v>0.02986055053770542</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.02356406487524509</c:v>
+                  <c:v>0.02388844080269337</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.02356406487524509</c:v>
+                  <c:v>0.02388844080269337</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.02356406487524509</c:v>
+                  <c:v>0.02388844080269337</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.01767304912209511</c:v>
+                  <c:v>0.01791633106768131</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.01178203243762255</c:v>
+                  <c:v>0.01194422040134668</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.01178203243762255</c:v>
+                  <c:v>0.01194422040134668</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.01178203243762255</c:v>
+                  <c:v>0.01194422040134668</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.01178203243762255</c:v>
+                  <c:v>0.01194422040134668</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.005891016218811274</c:v>
+                  <c:v>0.005972110200673342</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.005891016218811274</c:v>
+                  <c:v>0.005972110200673342</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.005891016218811274</c:v>
+                  <c:v>0.005972110200673342</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.005891016218811274</c:v>
+                  <c:v>0.005972110200673342</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.005891016218811274</c:v>
+                  <c:v>0.005972110200673342</c:v>
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>0</c:v>
@@ -1717,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>37.26346588134766</v>
+        <v>35.57202529907227</v>
       </c>
       <c r="C3" s="1">
         <v>1536</v>
@@ -1743,7 +1749,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>24.86656951904297</v>
+        <v>23.73784065246582</v>
       </c>
       <c r="C4" s="1">
         <v>1025</v>
@@ -1769,25 +1775,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>11.79039287567139</v>
+        <v>12.78369617462158</v>
       </c>
       <c r="C5" s="1">
-        <v>486</v>
+        <v>552</v>
       </c>
       <c r="D5" s="1">
+        <v>788</v>
+      </c>
+      <c r="E5" s="1">
+        <v>788</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
         <v>552</v>
-      </c>
-      <c r="E5" s="1">
-        <v>552</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1">
-        <v>486</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1795,16 +1801,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>8.733624458312988</v>
+        <v>11.25521087646484</v>
       </c>
       <c r="C6" s="1">
-        <v>360</v>
+        <v>486</v>
       </c>
       <c r="D6" s="1">
-        <v>660</v>
+        <v>552</v>
       </c>
       <c r="E6" s="1">
-        <v>660</v>
+        <v>552</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1813,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>360</v>
+        <v>486</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1821,16 +1827,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>6.234837532043457</v>
+        <v>5.951829433441162</v>
       </c>
       <c r="C7" s="1">
         <v>257</v>
       </c>
       <c r="D7" s="1">
-        <v>2836</v>
+        <v>2720</v>
       </c>
       <c r="E7" s="1">
-        <v>2836</v>
+        <v>2720</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -1847,7 +1853,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>4.366812229156494</v>
+        <v>4.168596744537354</v>
       </c>
       <c r="C8" s="1">
         <v>180</v>
@@ -1873,7 +1879,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>2.328966617584229</v>
+        <v>2.223251581192017</v>
       </c>
       <c r="C9" s="1">
         <v>96</v>
@@ -1899,7 +1905,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>2.328966617584229</v>
+        <v>2.223251581192017</v>
       </c>
       <c r="C10" s="1">
         <v>96</v>
@@ -1925,7 +1931,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>1.746724843978882</v>
+        <v>1.667438626289368</v>
       </c>
       <c r="C11" s="1">
         <v>72</v>
@@ -1951,7 +1957,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.2183406054973602</v>
+        <v>0.208429828286171</v>
       </c>
       <c r="C12" s="1">
         <v>9</v>
@@ -1977,7 +1983,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09704027324914932</v>
+        <v>0.09263548254966736</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
@@ -2003,25 +2009,51 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.02426006831228733</v>
+        <v>0.09263548254966736</v>
       </c>
       <c r="C14" s="1">
+        <v>4</v>
+      </c>
+      <c r="D14" s="1">
+        <v>462</v>
+      </c>
+      <c r="E14" s="1">
+        <v>462</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.02315887063741684</v>
+      </c>
+      <c r="C15" s="1">
         <v>1</v>
       </c>
-      <c r="D14" s="1">
-        <v>263</v>
-      </c>
-      <c r="E14" s="1">
-        <v>262</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
+      <c r="D15" s="1">
+        <v>198</v>
+      </c>
+      <c r="E15" s="1">
+        <v>198</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
         <v>1</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -2110,7 +2142,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>23.55522918701172</v>
+        <v>23.87948226928711</v>
       </c>
       <c r="C3" s="1">
         <v>7997</v>
@@ -2133,10 +2165,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2">
-        <v>9.997054100036621</v>
+        <v>10.13467121124268</v>
       </c>
       <c r="C4" s="1">
         <v>3394</v>
@@ -2162,16 +2194,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>8.353461265563965</v>
+        <v>8.1220703125</v>
       </c>
       <c r="C5" s="1">
-        <v>2836</v>
+        <v>2720</v>
       </c>
       <c r="D5" s="1">
         <v>257</v>
       </c>
       <c r="E5" s="1">
-        <v>2836</v>
+        <v>2720</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -2185,10 +2217,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2">
-        <v>6.238585948944092</v>
+        <v>6.324464797973633</v>
       </c>
       <c r="C6" s="1">
         <v>2118</v>
@@ -2211,10 +2243,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2">
-        <v>5.702503681182861</v>
+        <v>5.781002521514893</v>
       </c>
       <c r="C7" s="1">
         <v>1936</v>
@@ -2237,19 +2269,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2">
-        <v>5.142857074737549</v>
+        <v>4.132700443267822</v>
       </c>
       <c r="C8" s="1">
-        <v>1746</v>
+        <v>1384</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>1746</v>
+        <v>1384</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -2263,19 +2295,19 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2">
-        <v>4.076583385467529</v>
+        <v>3.427991390228272</v>
       </c>
       <c r="C9" s="1">
-        <v>1384</v>
+        <v>1148</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>1384</v>
+        <v>1148</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -2289,10 +2321,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2">
-        <v>3.098674535751343</v>
+        <v>3.141330003738403</v>
       </c>
       <c r="C10" s="1">
         <v>1052</v>
@@ -2315,10 +2347,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2">
-        <v>3.092783451080322</v>
+        <v>3.135357856750488</v>
       </c>
       <c r="C11" s="1">
         <v>1050</v>
@@ -2341,10 +2373,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2">
-        <v>2.362297534942627</v>
+        <v>2.394816160202026</v>
       </c>
       <c r="C12" s="1">
         <v>802</v>
@@ -2367,10 +2399,10 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2">
-        <v>2.321060419082642</v>
+        <v>2.3530113697052</v>
       </c>
       <c r="C13" s="1">
         <v>788</v>
@@ -2393,19 +2425,19 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" s="2">
-        <v>1.944035291671753</v>
+        <v>2.3530113697052</v>
       </c>
       <c r="C14" s="1">
-        <v>660</v>
+        <v>788</v>
       </c>
       <c r="D14" s="1">
-        <v>360</v>
+        <v>552</v>
       </c>
       <c r="E14" s="1">
-        <v>660</v>
+        <v>788</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -2414,15 +2446,15 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>360</v>
+        <v>552</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>1.625920414924622</v>
+        <v>1.648302435874939</v>
       </c>
       <c r="C15" s="1">
         <v>552</v>
@@ -2445,54 +2477,54 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>1.425625920295715</v>
+        <v>1.397473812103272</v>
       </c>
       <c r="C16" s="1">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>1536</v>
       </c>
       <c r="E16" s="1">
-        <v>484</v>
+        <v>64</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2">
-        <v>1.378497838973999</v>
+        <v>1.379557490348816</v>
       </c>
       <c r="C17" s="1">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="D17" s="1">
-        <v>1536</v>
+        <v>4</v>
       </c>
       <c r="E17" s="1">
-        <v>64</v>
+        <v>462</v>
       </c>
       <c r="F17" s="1">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>1536</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2500,7 +2532,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="2">
-        <v>1.278350472450256</v>
+        <v>1.295947909355164</v>
       </c>
       <c r="C18" s="1">
         <v>434</v>
@@ -2526,7 +2558,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="2">
-        <v>1.204712867736816</v>
+        <v>1.221296548843384</v>
       </c>
       <c r="C19" s="1">
         <v>409</v>
@@ -2552,7 +2584,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="2">
-        <v>1.107511043548584</v>
+        <v>1.122756719589233</v>
       </c>
       <c r="C20" s="1">
         <v>376</v>
@@ -2578,7 +2610,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="2">
-        <v>0.9779086709022522</v>
+        <v>0.9913703203201294</v>
       </c>
       <c r="C21" s="1">
         <v>332</v>
@@ -2604,7 +2636,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="2">
-        <v>0.9307805299758911</v>
+        <v>0.943593442440033</v>
       </c>
       <c r="C22" s="1">
         <v>316</v>
@@ -2627,25 +2659,25 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B23" s="2">
-        <v>0.7746686339378357</v>
+        <v>0.9197049736976624</v>
       </c>
       <c r="C23" s="1">
-        <v>263</v>
+        <v>308</v>
       </c>
       <c r="D23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
@@ -2653,10 +2685,10 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="2">
-        <v>0.7717231512069702</v>
+        <v>0.7823464274406433</v>
       </c>
       <c r="C24" s="1">
         <v>262</v>
@@ -2682,7 +2714,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="2">
-        <v>0.7599411010742188</v>
+        <v>0.770402193069458</v>
       </c>
       <c r="C25" s="1">
         <v>258</v>
@@ -2705,10 +2737,10 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" s="2">
-        <v>0.7069219350814819</v>
+        <v>0.7166532278060913</v>
       </c>
       <c r="C26" s="1">
         <v>240</v>
@@ -2734,7 +2766,7 @@
         <v>10</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6391752362251282</v>
+        <v>0.6479739546775818</v>
       </c>
       <c r="C27" s="1">
         <v>217</v>
@@ -2760,7 +2792,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="2">
-        <v>0.5832105875015259</v>
+        <v>0.5912389159202576</v>
       </c>
       <c r="C28" s="1">
         <v>198</v>
@@ -2783,28 +2815,28 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B29" s="2">
-        <v>0.5773195624351502</v>
+        <v>0.5912389159202576</v>
       </c>
       <c r="C29" s="1">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="1">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F29" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -2812,19 +2844,19 @@
         <v>31</v>
       </c>
       <c r="B30" s="2">
-        <v>0.5714285969734192</v>
+        <v>0.5852668285369873</v>
       </c>
       <c r="C30" s="1">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
@@ -2838,19 +2870,19 @@
         <v>32</v>
       </c>
       <c r="B31" s="2">
-        <v>0.553755521774292</v>
+        <v>0.5792946815490723</v>
       </c>
       <c r="C31" s="1">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="F31" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -2864,19 +2896,19 @@
         <v>33</v>
       </c>
       <c r="B32" s="2">
-        <v>0.5243004560470581</v>
+        <v>0.5613783597946167</v>
       </c>
       <c r="C32" s="1">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -2890,16 +2922,16 @@
         <v>34</v>
       </c>
       <c r="B33" s="2">
-        <v>0.4064801037311554</v>
+        <v>0.5315178036689758</v>
       </c>
       <c r="C33" s="1">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2916,16 +2948,16 @@
         <v>35</v>
       </c>
       <c r="B34" s="2">
-        <v>0.3770250380039215</v>
+        <v>0.4658246040344238</v>
       </c>
       <c r="C34" s="1">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2939,19 +2971,19 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B35" s="2">
-        <v>0.3770250380039215</v>
+        <v>0.4120756089687347</v>
       </c>
       <c r="C35" s="1">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D35" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2960,15 +2992,15 @@
         <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B36" s="2">
-        <v>0.3770250380039215</v>
+        <v>0.3822150528430939</v>
       </c>
       <c r="C36" s="1">
         <v>128</v>
@@ -2991,19 +3023,19 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="B37" s="2">
-        <v>0.3652430176734924</v>
+        <v>0.3822150528430939</v>
       </c>
       <c r="C37" s="1">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D37" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E37" s="1">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -3012,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -3020,7 +3052,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="2">
-        <v>0.3652430176734924</v>
+        <v>0.370270848274231</v>
       </c>
       <c r="C38" s="1">
         <v>124</v>
@@ -3046,7 +3078,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="2">
-        <v>0.3652430176734924</v>
+        <v>0.370270848274231</v>
       </c>
       <c r="C39" s="1">
         <v>124</v>
@@ -3072,7 +3104,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="2">
-        <v>0.353460967540741</v>
+        <v>0.3583266139030457</v>
       </c>
       <c r="C40" s="1">
         <v>120</v>
@@ -3098,7 +3130,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>0.3298968970775604</v>
+        <v>0.3344381749629974</v>
       </c>
       <c r="C41" s="1">
         <v>112</v>
@@ -3124,7 +3156,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="2">
-        <v>0.276877760887146</v>
+        <v>0.2806891798973084</v>
       </c>
       <c r="C42" s="1">
         <v>94</v>
@@ -3150,7 +3182,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="2">
-        <v>0.2415316700935364</v>
+        <v>0.244856521487236</v>
       </c>
       <c r="C43" s="1">
         <v>82</v>
@@ -3176,7 +3208,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="2">
-        <v>0.2297496348619461</v>
+        <v>0.2329123020172119</v>
       </c>
       <c r="C44" s="1">
         <v>78</v>
@@ -3202,7 +3234,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="2">
-        <v>0.2297496348619461</v>
+        <v>0.2329123020172119</v>
       </c>
       <c r="C45" s="1">
         <v>78</v>
@@ -3228,7 +3260,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2179675996303558</v>
+        <v>0.2209680825471878</v>
       </c>
       <c r="C46" s="1">
         <v>74</v>
@@ -3254,7 +3286,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2120765894651413</v>
+        <v>0.2149959653615952</v>
       </c>
       <c r="C47" s="1">
         <v>72</v>
@@ -3280,7 +3312,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2120765894651413</v>
+        <v>0.2149959653615952</v>
       </c>
       <c r="C48" s="1">
         <v>72</v>
@@ -3306,7 +3338,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="2">
-        <v>0.1767304837703705</v>
+        <v>0.1791633069515228</v>
       </c>
       <c r="C49" s="1">
         <v>60</v>
@@ -3332,7 +3364,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="2">
-        <v>0.1649484485387802</v>
+        <v>0.1672190874814987</v>
       </c>
       <c r="C50" s="1">
         <v>56</v>
@@ -3358,7 +3390,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="2">
-        <v>0.1413843929767609</v>
+        <v>0.1433306485414505</v>
       </c>
       <c r="C51" s="1">
         <v>48</v>
@@ -3384,7 +3416,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="2">
-        <v>0.1413843929767609</v>
+        <v>0.1433306485414505</v>
       </c>
       <c r="C52" s="1">
         <v>48</v>
@@ -3410,7 +3442,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="2">
-        <v>0.1413843929767609</v>
+        <v>0.1433306485414505</v>
       </c>
       <c r="C53" s="1">
         <v>48</v>
@@ -3436,7 +3468,7 @@
         <v>11</v>
       </c>
       <c r="B54" s="2">
-        <v>0.1354933679103851</v>
+        <v>0.1373585313558579</v>
       </c>
       <c r="C54" s="1">
         <v>46</v>
@@ -3462,7 +3494,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2">
-        <v>0.1296023577451706</v>
+        <v>0.1313864290714264</v>
       </c>
       <c r="C55" s="1">
         <v>44</v>
@@ -3488,7 +3520,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>0.1296023577451706</v>
+        <v>0.1313864290714264</v>
       </c>
       <c r="C56" s="1">
         <v>44</v>
@@ -3514,7 +3546,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2">
-        <v>0.1178203225135803</v>
+        <v>0.1194422021508217</v>
       </c>
       <c r="C57" s="1">
         <v>40</v>
@@ -3540,7 +3572,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2">
-        <v>0.1060382947325707</v>
+        <v>0.1074979826807976</v>
       </c>
       <c r="C58" s="1">
         <v>36</v>
@@ -3566,7 +3598,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="2">
-        <v>0.1001472771167755</v>
+        <v>0.1015258729457855</v>
       </c>
       <c r="C59" s="1">
         <v>34</v>
@@ -3592,7 +3624,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2">
-        <v>0.1001472771167755</v>
+        <v>0.1015258729457855</v>
       </c>
       <c r="C60" s="1">
         <v>34</v>
@@ -3618,7 +3650,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="2">
-        <v>0.08247422426939011</v>
+        <v>0.08360954374074936</v>
       </c>
       <c r="C61" s="1">
         <v>28</v>
@@ -3644,7 +3676,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="2">
-        <v>0.08247422426939011</v>
+        <v>0.08360954374074936</v>
       </c>
       <c r="C62" s="1">
         <v>28</v>
@@ -3670,7 +3702,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="2">
-        <v>0.07658321410417557</v>
+        <v>0.07763743400573731</v>
       </c>
       <c r="C63" s="1">
         <v>26</v>
@@ -3696,7 +3728,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="2">
-        <v>0.07658321410417557</v>
+        <v>0.07763743400573731</v>
       </c>
       <c r="C64" s="1">
         <v>26</v>
@@ -3722,7 +3754,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="2">
-        <v>0.05301914736628532</v>
+        <v>0.05374899134039879</v>
       </c>
       <c r="C65" s="1">
         <v>18</v>
@@ -3748,7 +3780,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="2">
-        <v>0.04712812975049019</v>
+        <v>0.04777688160538673</v>
       </c>
       <c r="C66" s="1">
         <v>16</v>
@@ -3774,7 +3806,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="2">
-        <v>0.04712812975049019</v>
+        <v>0.04777688160538673</v>
       </c>
       <c r="C67" s="1">
         <v>16</v>
@@ -3800,7 +3832,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="2">
-        <v>0.04123711213469505</v>
+        <v>0.04180477187037468</v>
       </c>
       <c r="C68" s="1">
         <v>14</v>
@@ -3826,7 +3858,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="2">
-        <v>0.03534609824419022</v>
+        <v>0.03583266213536263</v>
       </c>
       <c r="C69" s="1">
         <v>12</v>
@@ -3852,7 +3884,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="2">
-        <v>0.03534609824419022</v>
+        <v>0.03583266213536263</v>
       </c>
       <c r="C70" s="1">
         <v>12</v>
@@ -3878,7 +3910,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="2">
-        <v>0.02945508062839508</v>
+        <v>0.02986055053770542</v>
       </c>
       <c r="C71" s="1">
         <v>10</v>
@@ -3904,7 +3936,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2">
-        <v>0.02945508062839508</v>
+        <v>0.02986055053770542</v>
       </c>
       <c r="C72" s="1">
         <v>10</v>
@@ -3930,7 +3962,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="2">
-        <v>0.02945508062839508</v>
+        <v>0.02986055053770542</v>
       </c>
       <c r="C73" s="1">
         <v>10</v>
@@ -3956,7 +3988,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="2">
-        <v>0.02356406487524509</v>
+        <v>0.02388844080269337</v>
       </c>
       <c r="C74" s="1">
         <v>8</v>
@@ -3982,7 +4014,7 @@
         <v>8</v>
       </c>
       <c r="B75" s="2">
-        <v>0.02356406487524509</v>
+        <v>0.02388844080269337</v>
       </c>
       <c r="C75" s="1">
         <v>8</v>
@@ -4008,7 +4040,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="2">
-        <v>0.02356406487524509</v>
+        <v>0.02388844080269337</v>
       </c>
       <c r="C76" s="1">
         <v>8</v>
@@ -4034,7 +4066,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C77" s="1">
         <v>6</v>
@@ -4060,7 +4092,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C78" s="1">
         <v>6</v>
@@ -4086,7 +4118,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C79" s="1">
         <v>6</v>
@@ -4112,7 +4144,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C80" s="1">
         <v>6</v>
@@ -4138,7 +4170,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C81" s="1">
         <v>6</v>
@@ -4164,7 +4196,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C82" s="1">
         <v>6</v>
@@ -4190,7 +4222,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C83" s="1">
         <v>6</v>
@@ -4216,7 +4248,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C84" s="1">
         <v>6</v>
@@ -4242,7 +4274,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C85" s="1">
         <v>6</v>
@@ -4268,7 +4300,7 @@
         <v>84</v>
       </c>
       <c r="B86" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C86" s="1">
         <v>6</v>
@@ -4294,7 +4326,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C87" s="1">
         <v>6</v>
@@ -4320,7 +4352,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C88" s="1">
         <v>6</v>
@@ -4346,7 +4378,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C89" s="1">
         <v>6</v>
@@ -4372,7 +4404,7 @@
         <v>88</v>
       </c>
       <c r="B90" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C90" s="1">
         <v>6</v>
@@ -4398,7 +4430,7 @@
         <v>89</v>
       </c>
       <c r="B91" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C91" s="1">
         <v>6</v>
@@ -4424,7 +4456,7 @@
         <v>90</v>
       </c>
       <c r="B92" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C92" s="1">
         <v>6</v>
@@ -4450,7 +4482,7 @@
         <v>91</v>
       </c>
       <c r="B93" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C93" s="1">
         <v>6</v>
@@ -4476,7 +4508,7 @@
         <v>92</v>
       </c>
       <c r="B94" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C94" s="1">
         <v>6</v>
@@ -4502,7 +4534,7 @@
         <v>93</v>
       </c>
       <c r="B95" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C95" s="1">
         <v>6</v>
@@ -4528,7 +4560,7 @@
         <v>94</v>
       </c>
       <c r="B96" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C96" s="1">
         <v>6</v>
@@ -4554,7 +4586,7 @@
         <v>95</v>
       </c>
       <c r="B97" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C97" s="1">
         <v>6</v>
@@ -4580,7 +4612,7 @@
         <v>96</v>
       </c>
       <c r="B98" s="2">
-        <v>0.01767304912209511</v>
+        <v>0.01791633106768131</v>
       </c>
       <c r="C98" s="1">
         <v>6</v>
@@ -4606,7 +4638,7 @@
         <v>97</v>
       </c>
       <c r="B99" s="2">
-        <v>0.01178203243762255</v>
+        <v>0.01194422040134668</v>
       </c>
       <c r="C99" s="1">
         <v>4</v>
@@ -4632,7 +4664,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="2">
-        <v>0.01178203243762255</v>
+        <v>0.01194422040134668</v>
       </c>
       <c r="C100" s="1">
         <v>4</v>
@@ -4658,7 +4690,7 @@
         <v>99</v>
       </c>
       <c r="B101" s="2">
-        <v>0.01178203243762255</v>
+        <v>0.01194422040134668</v>
       </c>
       <c r="C101" s="1">
         <v>4</v>
@@ -4684,7 +4716,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="2">
-        <v>0.01178203243762255</v>
+        <v>0.01194422040134668</v>
       </c>
       <c r="C102" s="1">
         <v>4</v>
@@ -4710,7 +4742,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="2">
-        <v>0.005891016218811274</v>
+        <v>0.005972110200673342</v>
       </c>
       <c r="C103" s="1">
         <v>2</v>
@@ -4736,7 +4768,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="2">
-        <v>0.005891016218811274</v>
+        <v>0.005972110200673342</v>
       </c>
       <c r="C104" s="1">
         <v>2</v>
@@ -4762,7 +4794,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="2">
-        <v>0.005891016218811274</v>
+        <v>0.005972110200673342</v>
       </c>
       <c r="C105" s="1">
         <v>2</v>
@@ -4788,7 +4820,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="2">
-        <v>0.005891016218811274</v>
+        <v>0.005972110200673342</v>
       </c>
       <c r="C106" s="1">
         <v>2</v>
@@ -4814,7 +4846,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="2">
-        <v>0.005891016218811274</v>
+        <v>0.005972110200673342</v>
       </c>
       <c r="C107" s="1">
         <v>2</v>

--- a/MDK-ARM/F401RC_analysis.xlsx
+++ b/MDK-ARM/F401RC_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="181">
   <si>
     <t>F401RC</t>
   </si>
@@ -32,21 +32,24 @@
     <t>st7789.o</t>
   </si>
   <si>
+    <t>spi.o</t>
+  </si>
+  <si>
+    <t>lv_gc.o</t>
+  </si>
+  <si>
+    <t>main.o</t>
+  </si>
+  <si>
+    <t>usart.o</t>
+  </si>
+  <si>
+    <t>lv_draw_sw_letter.o</t>
+  </si>
+  <si>
     <t>usart_idel_config.o</t>
   </si>
   <si>
-    <t>lv_gc.o</t>
-  </si>
-  <si>
-    <t>spi.o</t>
-  </si>
-  <si>
-    <t>usart.o</t>
-  </si>
-  <si>
-    <t>lv_draw_sw_letter.o</t>
-  </si>
-  <si>
     <t>i2c.o</t>
   </si>
   <si>
@@ -80,6 +83,9 @@
     <t>lv_timer.o</t>
   </si>
   <si>
+    <t>setup_scr_screen.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal.o</t>
   </si>
   <si>
@@ -113,6 +119,12 @@
     <t>lv_font_montserrat_14.o</t>
   </si>
   <si>
+    <t>lv_font_alatsi_regular_29.o</t>
+  </si>
+  <si>
+    <t>lv_font_alatsi_regular_13.o</t>
+  </si>
+  <si>
     <t>lv_style.o</t>
   </si>
   <si>
@@ -122,6 +134,12 @@
     <t>lv_obj.o</t>
   </si>
   <si>
+    <t>strtok.o</t>
+  </si>
+  <si>
+    <t>widgets_init.o</t>
+  </si>
+  <si>
     <t>system_stm32f4xx.o</t>
   </si>
   <si>
@@ -143,6 +161,9 @@
     <t>lv_win.o</t>
   </si>
   <si>
+    <t>w25qxx.o</t>
+  </si>
+  <si>
     <t>lv_obj_style.o</t>
   </si>
   <si>
@@ -182,6 +203,9 @@
     <t>lv_roller.o</t>
   </si>
   <si>
+    <t>stm32f4xx_hal_spi.o</t>
+  </si>
+  <si>
     <t>lv_img.o</t>
   </si>
   <si>
@@ -224,24 +248,27 @@
     <t>lv_tlsf.o</t>
   </si>
   <si>
+    <t>lv_calendar.o</t>
+  </si>
+  <si>
     <t>lv_draw_sw_img.o</t>
   </si>
   <si>
-    <t>stm32f4xx_hal_spi.o</t>
-  </si>
-  <si>
-    <t>lv_calendar.o</t>
-  </si>
-  <si>
     <t>lv_draw_arc.o</t>
   </si>
   <si>
+    <t>lv_disp.o</t>
+  </si>
+  <si>
     <t>lv_calendar_header_dropdown.o</t>
   </si>
   <si>
     <t>stm32f4xx_hal_dma.o</t>
   </si>
   <si>
+    <t>lv_dclock.o</t>
+  </si>
+  <si>
     <t>lv_obj_tree.o</t>
   </si>
   <si>
@@ -269,6 +296,9 @@
     <t>lv_draw_sw_polygon.o</t>
   </si>
   <si>
+    <t>fz_wm.l</t>
+  </si>
+  <si>
     <t>lv_math.o</t>
   </si>
   <si>
@@ -299,7 +329,10 @@
     <t>lv_ll.o</t>
   </si>
   <si>
-    <t>main.o</t>
+    <t>dmul.o</t>
+  </si>
+  <si>
+    <t>lc_ctype_c.o</t>
   </si>
   <si>
     <t>gpio.o</t>
@@ -314,6 +347,9 @@
     <t>lludivv7m.o</t>
   </si>
   <si>
+    <t>lv_obj_style_gen.o</t>
+  </si>
+  <si>
     <t>lv_font.o</t>
   </si>
   <si>
@@ -323,13 +359,19 @@
     <t>lv_draw_layer.o</t>
   </si>
   <si>
-    <t>lv_obj_style_gen.o</t>
+    <t>stm32f4xx_it.o</t>
+  </si>
+  <si>
+    <t>_strtoul.o</t>
+  </si>
+  <si>
+    <t>dnaninf.o</t>
   </si>
   <si>
     <t>rt_memcpy_v6.o</t>
   </si>
   <si>
-    <t>stm32f4xx_it.o</t>
+    <t>dma.o</t>
   </si>
   <si>
     <t>strcmpv7em.o</t>
@@ -338,18 +380,18 @@
     <t>lv_theme.o</t>
   </si>
   <si>
+    <t>strtol.o</t>
+  </si>
+  <si>
     <t>lv_draw_rect.o</t>
   </si>
   <si>
-    <t>lv_disp.o</t>
-  </si>
-  <si>
-    <t>dma.o</t>
-  </si>
-  <si>
     <t>rt_memcpy_w.o</t>
   </si>
   <si>
+    <t>dfix.o</t>
+  </si>
+  <si>
     <t>__scatter.o</t>
   </si>
   <si>
@@ -371,6 +413,9 @@
     <t>strcpy.o</t>
   </si>
   <si>
+    <t>strtok_int.o</t>
+  </si>
+  <si>
     <t>lv_utils.o</t>
   </si>
   <si>
@@ -389,24 +434,45 @@
     <t>lv_draw_transform.o</t>
   </si>
   <si>
+    <t>dflt_clz.o</t>
+  </si>
+  <si>
     <t>lv_draw_line.o</t>
   </si>
   <si>
+    <t>strcspn.o</t>
+  </si>
+  <si>
+    <t>strspn.o</t>
+  </si>
+  <si>
+    <t>_chval.o</t>
+  </si>
+  <si>
     <t>__scatter_zi.o</t>
   </si>
   <si>
-    <t>fz_wm.l</t>
-  </si>
-  <si>
     <t>fpinit.o</t>
   </si>
   <si>
+    <t>atoi.o</t>
+  </si>
+  <si>
     <t>__scatter_copy.o</t>
   </si>
   <si>
+    <t>libinit2.o</t>
+  </si>
+  <si>
+    <t>gui_guider.o</t>
+  </si>
+  <si>
     <t>exit.o</t>
   </si>
   <si>
+    <t>rt_ctype_table.o</t>
+  </si>
+  <si>
     <t>aeabi_memset4.o</t>
   </si>
   <si>
@@ -416,6 +482,9 @@
     <t>lv_extra.o</t>
   </si>
   <si>
+    <t>dretinf.o</t>
+  </si>
+  <si>
     <t>sys_exit.o</t>
   </si>
   <si>
@@ -428,10 +497,13 @@
     <t>lv_draw.o</t>
   </si>
   <si>
+    <t>rt_locale_intlibspace.o</t>
+  </si>
+  <si>
+    <t>rt_errno_addr_intlibspace.o</t>
+  </si>
+  <si>
     <t>__main.o</t>
-  </si>
-  <si>
-    <t>libinit2.o</t>
   </si>
   <si>
     <t>heapauxi.o</t>
@@ -575,9 +647,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$148</c:f>
+              <c:f>ram_percent!$A$3:$A$172</c:f>
               <c:strCache>
-                <c:ptCount val="146"/>
+                <c:ptCount val="170"/>
                 <c:pt idx="0">
                   <c:v>startup_stm32f401xc.o</c:v>
                 </c:pt>
@@ -591,13 +663,13 @@
                   <c:v>st7789.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>usart_idel_config.o</c:v>
+                  <c:v>spi.o</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>lv_gc.o</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>spi.o</c:v>
+                  <c:v>main.o</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>usart.o</c:v>
@@ -606,105 +678,126 @@
                   <c:v>lv_draw_sw_letter.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>usart_idel_config.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>lv_theme_default.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>c_w.l</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>lv_keyboard.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>lv_refr.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>lv_txt.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>lv_btnmatrix.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>lv_grid.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>lv_timer.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
+                  <c:v>setup_scr_screen.o</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>lv_tileview.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="24">
                   <c:v>lv_flex.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="25">
                   <c:v>lv_draw_sw_gradient.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="26">
                   <c:v>lv_area.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="27">
                   <c:v>lv_anim.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="28">
                   <c:v>lv_colorwheel.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="29">
                   <c:v>lv_spinner.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>lv_indev.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>lv_hal_tick.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="32">
                   <c:v>lv_font_montserrat_14.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="33">
+                  <c:v>lv_font_alatsi_regular_29.o</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>lv_font_alatsi_regular_13.o</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>lv_style.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="36">
                   <c:v>lv_obj_pos.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="37">
                   <c:v>lv_obj.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="38">
+                  <c:v>strtok.o</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>widgets_init.o</c:v>
+                </c:pt>
+                <c:pt idx="40">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="41">
                   <c:v>lv_textarea.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="42">
                   <c:v>lv_tabview.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="43">
                   <c:v>lv_hal_disp.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="44">
                   <c:v>lv_group.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="45">
                   <c:v>lv_event.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="46">
                   <c:v>lv_win.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="47">
+                  <c:v>w25qxx.o</c:v>
+                </c:pt>
+                <c:pt idx="48">
                   <c:v>lv_obj_style.o</c:v>
                 </c:pt>
-                <c:pt idx="145">
+                <c:pt idx="169">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -712,137 +805,158 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$148</c:f>
+              <c:f>ram_percent!$B$3:$B$172</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="146"/>
+                <c:ptCount val="170"/>
                 <c:pt idx="0">
-                  <c:v>54.89635467529297</c:v>
+                  <c:v>54.89880752563477</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22.90922164916992</c:v>
+                  <c:v>22.91024398803711</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.391440391540527</c:v>
+                  <c:v>7.391770362854004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.150196552276611</c:v>
+                  <c:v>7.152750015258789</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.287348031997681</c:v>
+                  <c:v>1.233078718185425</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.188348770141602</c:v>
+                  <c:v>1.188401937484741</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.8041458129882813</c:v>
+                  <c:v>1.179466605186462</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.7505360841751099</c:v>
+                  <c:v>0.7505696415901184</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.5897069573402405</c:v>
+                  <c:v>0.5897333025932312</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.4020729064941406</c:v>
+                  <c:v>0.5718625783920288</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2412437498569489</c:v>
+                  <c:v>0.4020908772945404</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2144388854503632</c:v>
+                  <c:v>0.241254523396492</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2144388854503632</c:v>
+                  <c:v>0.2233838140964508</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.1608291566371918</c:v>
+                  <c:v>0.2144484668970108</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.1608291566371918</c:v>
+                  <c:v>0.1608363538980484</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.07147962599992752</c:v>
+                  <c:v>0.1608363538980484</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.06254467368125916</c:v>
+                  <c:v>0.0714828222990036</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.06254467368125916</c:v>
+                  <c:v>0.062547467648983</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.04914224520325661</c:v>
+                  <c:v>0.062547467648983</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.04467476904392242</c:v>
+                  <c:v>0.0491444393992424</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.0268048606812954</c:v>
+                  <c:v>0.0446767620742321</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.0268048606812954</c:v>
+                  <c:v>0.0357414111495018</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.0268048606812954</c:v>
+                  <c:v>0.02680605836212635</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.0268048606812954</c:v>
+                  <c:v>0.02680605836212635</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.0268048606812954</c:v>
+                  <c:v>0.02680605836212635</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.0268048606812954</c:v>
+                  <c:v>0.02680605836212635</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02010364457964897</c:v>
+                  <c:v>0.02680605836212635</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.01786990649998188</c:v>
+                  <c:v>0.02680605836212635</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.01786990649998188</c:v>
+                  <c:v>0.02010454423725605</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.01786990649998188</c:v>
+                  <c:v>0.0178707055747509</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.01786990649998188</c:v>
+                  <c:v>0.0178707055747509</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.0134024303406477</c:v>
+                  <c:v>0.0178707055747509</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.01116869226098061</c:v>
+                  <c:v>0.0178707055747509</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.01116869226098061</c:v>
+                  <c:v>0.0178707055747509</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.00893495324999094</c:v>
+                  <c:v>0.0178707055747509</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.00893495324999094</c:v>
+                  <c:v>0.01340302918106318</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.00893495324999094</c:v>
+                  <c:v>0.01116919051855803</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.00893495324999094</c:v>
+                  <c:v>0.01116919051855803</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.00893495324999094</c:v>
+                  <c:v>0.00893535278737545</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.00893495324999094</c:v>
+                  <c:v>0.00893535278737545</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.00446747662499547</c:v>
+                  <c:v>0.00893535278737545</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.002233738312497735</c:v>
-                </c:pt>
-                <c:pt idx="145">
+                  <c:v>0.00893535278737545</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.00893535278737545</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.00893535278737545</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.00893535278737545</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.00893535278737545</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.004467676393687725</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.002233838196843863</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.002233838196843863</c:v>
+                </c:pt>
+                <c:pt idx="169">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -910,445 +1024,517 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$148</c:f>
+              <c:f>flash_percent!$A$3:$A$172</c:f>
               <c:strCache>
-                <c:ptCount val="146"/>
+                <c:ptCount val="170"/>
                 <c:pt idx="0">
+                  <c:v>lv_font_alatsi_regular_29.o</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>lv_font_montserrat_14.o</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>lv_font_alatsi_regular_13.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>lv_theme_default.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>lv_chart.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>lv_draw_sw_rect.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>lv_obj_pos.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>lv_refr.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>lv_label.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>lv_obj_scroll.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>lv_draw_mask.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>lv_btnmatrix.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>lv_textarea.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>lv_draw_sw_blend.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>lv_obj_style.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
+                  <c:v>lv_obj.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>lv_dropdown.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>lv_obj.o</c:v>
-                </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>stm32f4xx_hal_i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>lv_arc.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>lv_draw_sw_arc.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>lv_table.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>lv_flex.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>lv_roller.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>lv_colorwheel.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="24">
                   <c:v>lv_grid.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="25">
+                  <c:v>stm32f4xx_hal_spi.o</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>lv_img.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="27">
                   <c:v>lv_meter.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="28">
                   <c:v>stm32f4xx_hal_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="29">
                   <c:v>lv_slider.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="30">
                   <c:v>lv_printf.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="31">
                   <c:v>lv_bar.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="32">
+                  <c:v>c_w.l</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>lv_img_decoder.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="34">
                   <c:v>lv_draw_sw_line.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="35">
                   <c:v>lv_keyboard.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="36">
                   <c:v>lv_txt.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="37">
                   <c:v>lv_obj_draw.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="38">
                   <c:v>lv_draw_sw_transform.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="39">
                   <c:v>lv_area.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="40">
                   <c:v>lv_draw_label.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="41">
                   <c:v>lv_draw_sw_letter.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="42">
                   <c:v>lv_menu.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="43">
                   <c:v>stm32f4xx_hal_rcc.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="44">
                   <c:v>lv_tlsf.o</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>lv_style.o</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>lv_draw_sw_img.o</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>stm32f4xx_hal_spi.o</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>c_w.l</c:v>
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>lv_calendar.o</c:v>
                 </c:pt>
                 <c:pt idx="46">
+                  <c:v>lv_style.o</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>lv_draw_sw_img.o</c:v>
+                </c:pt>
+                <c:pt idx="48">
                   <c:v>lv_draw_arc.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="49">
+                  <c:v>lv_disp.o</c:v>
+                </c:pt>
+                <c:pt idx="50">
                   <c:v>lv_calendar_header_dropdown.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="51">
                   <c:v>stm32f4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="52">
                   <c:v>lv_mem.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="53">
+                  <c:v>lv_dclock.o</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>lv_anim.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="55">
                   <c:v>lv_draw_sw_gradient.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="56">
                   <c:v>lv_tabview.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="57">
                   <c:v>lv_obj_tree.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="58">
                   <c:v>lv_spinbox.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="59">
                   <c:v>lv_checkbox.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="60">
                   <c:v>lv_group.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="61">
                   <c:v>lv_color.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="62">
                   <c:v>lv_draw_img.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="63">
                   <c:v>lv_fs.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
-                  <c:v>st7789.o</c:v>
-                </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="64">
                   <c:v>lv_switch.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="65">
                   <c:v>stm32f4xx_hal_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="66">
                   <c:v>lv_draw_sw_polygon.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
-                  <c:v>lv_event.o</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>lv_math.o</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>lv_font_fmt_txt.o</c:v>
-                </c:pt>
                 <c:pt idx="67">
-                  <c:v>lv_calendar_header_arrow.o</c:v>
+                  <c:v>fz_wm.l</c:v>
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>spi.o</c:v>
                 </c:pt>
                 <c:pt idx="69">
+                  <c:v>lv_event.o</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>st7789.o</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>lv_math.o</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>lv_font_fmt_txt.o</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>lv_calendar_header_arrow.o</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>widgets_init.o</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="76">
                   <c:v>lv_led.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="77">
                   <c:v>lv_hal_disp.o</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="78">
                   <c:v>lv_timer.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="79">
                   <c:v>startup_stm32f401xc.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="80">
+                  <c:v>setup_scr_screen.o</c:v>
+                </c:pt>
+                <c:pt idx="81">
                   <c:v>lv_draw_sw_layer.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="82">
                   <c:v>lv_line.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="83">
                   <c:v>stm32f4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="84">
                   <c:v>lv_obj_class.o</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="85">
                   <c:v>lv_tileview.o</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="86">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="79">
+                <c:pt idx="87">
                   <c:v>lv_style_gen.o</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="88">
                   <c:v>lv_ll.o</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="89">
                   <c:v>lv_indev.o</c:v>
                 </c:pt>
-                <c:pt idx="82">
-                  <c:v>main.o</c:v>
-                </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="90">
+                  <c:v>dmul.o</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>lc_ctype_c.o</c:v>
+                </c:pt>
+                <c:pt idx="92">
                   <c:v>gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="93">
                   <c:v>lv_img_buf.o</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="94">
                   <c:v>lv_draw_sw.o</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="95">
                   <c:v>lludivv7m.o</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="96">
+                  <c:v>lv_obj_style_gen.o</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="98">
                   <c:v>lv_font.o</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="99">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="100">
                   <c:v>stm32f4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="101">
                   <c:v>lv_port_disp.o</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="102">
                   <c:v>lv_draw_layer.o</c:v>
                 </c:pt>
-                <c:pt idx="93">
-                  <c:v>lv_obj_style_gen.o</c:v>
-                </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="103">
                   <c:v>lv_spinner.o</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="104">
                   <c:v>usart_idel_config.o</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="105">
+                  <c:v>stm32f4xx_it.o</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>_strtoul.o</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>dnaninf.o</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>lv_win.o</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="109">
                   <c:v>rt_memcpy_v6.o</c:v>
                 </c:pt>
-                <c:pt idx="98">
-                  <c:v>stm32f4xx_it.o</c:v>
-                </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="110">
+                  <c:v>dma.o</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>strcmpv7em.o</c:v>
                 </c:pt>
-                <c:pt idx="100">
+                <c:pt idx="112">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="101">
+                <c:pt idx="113">
                   <c:v>lv_theme.o</c:v>
                 </c:pt>
-                <c:pt idx="102">
+                <c:pt idx="114">
+                  <c:v>strtol.o</c:v>
+                </c:pt>
+                <c:pt idx="115">
                   <c:v>lv_draw_rect.o</c:v>
                 </c:pt>
-                <c:pt idx="103">
-                  <c:v>lv_disp.o</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>dma.o</c:v>
-                </c:pt>
-                <c:pt idx="105">
+                <c:pt idx="116">
                   <c:v>rt_memcpy_w.o</c:v>
                 </c:pt>
-                <c:pt idx="106">
+                <c:pt idx="117">
+                  <c:v>dfix.o</c:v>
+                </c:pt>
+                <c:pt idx="118">
                   <c:v>__scatter.o</c:v>
                 </c:pt>
-                <c:pt idx="107">
+                <c:pt idx="119">
                   <c:v>lv_img_cache.o</c:v>
                 </c:pt>
-                <c:pt idx="108">
+                <c:pt idx="120">
                   <c:v>lv_list.o</c:v>
                 </c:pt>
-                <c:pt idx="109">
+                <c:pt idx="121">
                   <c:v>rt_memclr_w.o</c:v>
                 </c:pt>
-                <c:pt idx="110">
+                <c:pt idx="122">
                   <c:v>lv_btn.o</c:v>
                 </c:pt>
-                <c:pt idx="111">
+                <c:pt idx="123">
                   <c:v>sys_stackheap_outer.o</c:v>
                 </c:pt>
-                <c:pt idx="112">
+                <c:pt idx="124">
                   <c:v>strcpy.o</c:v>
                 </c:pt>
-                <c:pt idx="113">
+                <c:pt idx="125">
+                  <c:v>w25qxx.o</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>strtok_int.o</c:v>
+                </c:pt>
+                <c:pt idx="127">
                   <c:v>lv_utils.o</c:v>
                 </c:pt>
-                <c:pt idx="114">
+                <c:pt idx="128">
                   <c:v>lv_indev_scroll.o</c:v>
                 </c:pt>
-                <c:pt idx="115">
+                <c:pt idx="129">
                   <c:v>strlen.o</c:v>
                 </c:pt>
-                <c:pt idx="116">
+                <c:pt idx="130">
                   <c:v>stm32f4xx_hal_msp.o</c:v>
                 </c:pt>
-                <c:pt idx="117">
+                <c:pt idx="131">
                   <c:v>lv_msgbox.o</c:v>
                 </c:pt>
-                <c:pt idx="118">
+                <c:pt idx="132">
                   <c:v>lv_draw_transform.o</c:v>
                 </c:pt>
-                <c:pt idx="119">
+                <c:pt idx="133">
                   <c:v>lv_hal_tick.o</c:v>
                 </c:pt>
-                <c:pt idx="120">
+                <c:pt idx="134">
+                  <c:v>dflt_clz.o</c:v>
+                </c:pt>
+                <c:pt idx="135">
                   <c:v>lv_draw_line.o</c:v>
                 </c:pt>
-                <c:pt idx="121">
+                <c:pt idx="136">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="122">
+                <c:pt idx="137">
+                  <c:v>strcspn.o</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>strspn.o</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>_chval.o</c:v>
+                </c:pt>
+                <c:pt idx="140">
                   <c:v>__scatter_zi.o</c:v>
                 </c:pt>
-                <c:pt idx="123">
-                  <c:v>fz_wm.l</c:v>
-                </c:pt>
-                <c:pt idx="124">
+                <c:pt idx="141">
                   <c:v>fpinit.o</c:v>
                 </c:pt>
-                <c:pt idx="125">
+                <c:pt idx="142">
+                  <c:v>atoi.o</c:v>
+                </c:pt>
+                <c:pt idx="143">
                   <c:v>__scatter_copy.o</c:v>
                 </c:pt>
-                <c:pt idx="126">
+                <c:pt idx="144">
+                  <c:v>libinit2.o</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>gui_guider.o</c:v>
+                </c:pt>
+                <c:pt idx="146">
                   <c:v>exit.o</c:v>
                 </c:pt>
-                <c:pt idx="127">
+                <c:pt idx="147">
+                  <c:v>strtok.o</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>rt_ctype_table.o</c:v>
+                </c:pt>
+                <c:pt idx="149">
                   <c:v>aeabi_memset4.o</c:v>
                 </c:pt>
-                <c:pt idx="128">
+                <c:pt idx="150">
                   <c:v>lv_hal_indev.o</c:v>
                 </c:pt>
-                <c:pt idx="129">
+                <c:pt idx="151">
                   <c:v>lv_extra.o</c:v>
                 </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="152">
+                  <c:v>dretinf.o</c:v>
+                </c:pt>
+                <c:pt idx="153">
                   <c:v>sys_exit.o</c:v>
                 </c:pt>
-                <c:pt idx="131">
+                <c:pt idx="154">
                   <c:v>__rtentry2.o</c:v>
                 </c:pt>
-                <c:pt idx="132">
+                <c:pt idx="155">
                   <c:v>rtexit2.o</c:v>
                 </c:pt>
-                <c:pt idx="133">
+                <c:pt idx="156">
                   <c:v>lv_draw.o</c:v>
                 </c:pt>
-                <c:pt idx="134">
+                <c:pt idx="157">
+                  <c:v>rt_locale_intlibspace.o</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>rt_errno_addr_intlibspace.o</c:v>
+                </c:pt>
+                <c:pt idx="159">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="135">
+                <c:pt idx="160">
                   <c:v>__main.o</c:v>
                 </c:pt>
-                <c:pt idx="136">
-                  <c:v>libinit2.o</c:v>
-                </c:pt>
-                <c:pt idx="137">
+                <c:pt idx="161">
                   <c:v>heapauxi.o</c:v>
                 </c:pt>
-                <c:pt idx="138">
+                <c:pt idx="162">
                   <c:v>__rtentry4.o</c:v>
                 </c:pt>
-                <c:pt idx="139">
+                <c:pt idx="163">
                   <c:v>stm32f4xx_hal_tim_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="140">
+                <c:pt idx="164">
                   <c:v>use_no_semi.o</c:v>
                 </c:pt>
-                <c:pt idx="141">
+                <c:pt idx="165">
                   <c:v>rtexit.o</c:v>
                 </c:pt>
-                <c:pt idx="142">
+                <c:pt idx="166">
                   <c:v>libshutdown2.o</c:v>
                 </c:pt>
-                <c:pt idx="143">
+                <c:pt idx="167">
                   <c:v>libshutdown.o</c:v>
                 </c:pt>
-                <c:pt idx="144">
+                <c:pt idx="168">
                   <c:v>libinit.o</c:v>
                 </c:pt>
-                <c:pt idx="145">
+                <c:pt idx="169">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1356,446 +1542,518 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$148</c:f>
+              <c:f>flash_percent!$B$3:$B$172</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="146"/>
+                <c:ptCount val="170"/>
                 <c:pt idx="0">
-                  <c:v>8.057757377624512</c:v>
+                  <c:v>16.18193435668945</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.949435710906982</c:v>
+                  <c:v>6.086921691894531</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.196440696716309</c:v>
+                  <c:v>4.832746982574463</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.917466163635254</c:v>
+                  <c:v>3.738860130310059</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.157378435134888</c:v>
+                  <c:v>3.170039176940918</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.650259256362915</c:v>
+                  <c:v>2.959298372268677</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.494222402572632</c:v>
+                  <c:v>2.385119676589966</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.483583688735962</c:v>
+                  <c:v>2.002035856246948</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.449302911758423</c:v>
+                  <c:v>1.884164094924927</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.377786159515381</c:v>
+                  <c:v>1.876127362251282</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.331093311309815</c:v>
+                  <c:v>1.850231289863586</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.192788124084473</c:v>
+                  <c:v>1.796206712722778</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.121271133422852</c:v>
+                  <c:v>1.760934352874756</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.94218373298645</c:v>
+                  <c:v>1.65645706653595</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.911449193954468</c:v>
+                  <c:v>1.602432489395142</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.906720757484436</c:v>
+                  <c:v>1.494829654693604</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.854708552360535</c:v>
+                  <c:v>1.467147707939148</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.71994960308075</c:v>
+                  <c:v>1.440358638763428</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.679758429527283</c:v>
+                  <c:v>1.401067972183228</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.624199867248535</c:v>
+                  <c:v>1.299269556999207</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.567459225654602</c:v>
+                  <c:v>1.268908619880676</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.510718703269959</c:v>
+                  <c:v>1.226939082145691</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.440974950790405</c:v>
+                  <c:v>1.184076547622681</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.262478470802307</c:v>
+                  <c:v>1.14121413230896</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.260114312171936</c:v>
+                  <c:v>1.088528871536255</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.211648344993591</c:v>
+                  <c:v>1.05906093120575</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.208102107048035</c:v>
+                  <c:v>0.9536906480789185</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.195098996162415</c:v>
+                  <c:v>0.9519047141075134</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.182096004486084</c:v>
+                  <c:v>0.9152929782867432</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.164364576339722</c:v>
+                  <c:v>0.9126140475273132</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.130083799362183</c:v>
+                  <c:v>0.902791440486908</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.110579133033752</c:v>
+                  <c:v>0.8929687738418579</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.085164070129395</c:v>
+                  <c:v>0.8849320411682129</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.01305627822876</c:v>
+                  <c:v>0.8795742392539978</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.9870501160621643</c:v>
+                  <c:v>0.8536781668663025</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.8889361619949341</c:v>
+                  <c:v>0.837158203125</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.8499270081520081</c:v>
+                  <c:v>0.8197453022003174</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.7813654541969299</c:v>
+                  <c:v>0.7652742266654968</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.776637077331543</c:v>
+                  <c:v>0.7456288933753967</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.7459025382995606</c:v>
+                  <c:v>0.6715124845504761</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.7364457845687866</c:v>
+                  <c:v>0.6420445442199707</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.6992097496986389</c:v>
+                  <c:v>0.5902523398399353</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.6915261745452881</c:v>
+                  <c:v>0.5866804718971252</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.6867977380752564</c:v>
+                  <c:v>0.5634632706642151</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.678523063659668</c:v>
+                  <c:v>0.556319534778595</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.6501528024673462</c:v>
+                  <c:v>0.5429250001907349</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.5934121608734131</c:v>
+                  <c:v>0.5281910300254822</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.5857285261154175</c:v>
+                  <c:v>0.5223867297172546</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.5815912485122681</c:v>
+                  <c:v>0.448270320892334</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.563859760761261</c:v>
+                  <c:v>0.4446984529495239</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.5555850863456726</c:v>
+                  <c:v>0.4424660205841065</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.5544030070304871</c:v>
+                  <c:v>0.4393406212329865</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.5295789837837219</c:v>
+                  <c:v>0.4259460866451263</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.5236685276031494</c:v>
+                  <c:v>0.4241601526737213</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.520122230052948</c:v>
+                  <c:v>0.4196953177452087</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.5165759325027466</c:v>
+                  <c:v>0.4188023507595062</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.489387720823288</c:v>
+                  <c:v>0.400050014257431</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.4621995389461517</c:v>
+                  <c:v>0.3955851495265961</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.4574711322784424</c:v>
+                  <c:v>0.3929062485694885</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.449196457862854</c:v>
+                  <c:v>0.390227347612381</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.4432860016822815</c:v>
+                  <c:v>0.3696890771389008</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.4385575950145721</c:v>
+                  <c:v>0.3491507768630981</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.4137336015701294</c:v>
+                  <c:v>0.3455789089202881</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.4078231155872345</c:v>
+                  <c:v>0.3393281400203705</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.3794527947902679</c:v>
+                  <c:v>0.3312914073467255</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.3629034757614136</c:v>
+                  <c:v>0.3125390708446503</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.3593571782112122</c:v>
+                  <c:v>0.3080742359161377</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.3380794525146484</c:v>
+                  <c:v>0.3009304702281952</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.3238942921161652</c:v>
+                  <c:v>0.29200080037117</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.3215301036834717</c:v>
+                  <c:v>0.2866429686546326</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.3203479945659638</c:v>
+                  <c:v>0.274141401052475</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.2990702688694</c:v>
+                  <c:v>0.274141401052475</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.2766104638576508</c:v>
+                  <c:v>0.2714625000953674</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.2706999778747559</c:v>
+                  <c:v>0.2661046981811523</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.2671536803245544</c:v>
+                  <c:v>0.2598538994789124</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.2636074125766754</c:v>
+                  <c:v>0.2464593797922134</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.2588790059089661</c:v>
+                  <c:v>0.2428874969482422</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.239965483546257</c:v>
+                  <c:v>0.2419945299625397</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.2352370917797089</c:v>
+                  <c:v>0.225921094417572</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.2127772718667984</c:v>
+                  <c:v>0.2089546918869019</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.2115951776504517</c:v>
+                  <c:v>0.2049363255500794</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.2021384090185165</c:v>
+                  <c:v>0.2044898420572281</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.1891353577375412</c:v>
+                  <c:v>0.2018109411001205</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.1477620005607605</c:v>
+                  <c:v>0.199132040143013</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.1465799063444138</c:v>
+                  <c:v>0.1955601572990418</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.145397812128067</c:v>
+                  <c:v>0.1812726557254791</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.1418515145778656</c:v>
+                  <c:v>0.1777007877826691</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.1371231377124786</c:v>
+                  <c:v>0.1607343703508377</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.1146633103489876</c:v>
+                  <c:v>0.1598414033651352</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.1111170202493668</c:v>
+                  <c:v>0.1526976525783539</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.1063886359333992</c:v>
+                  <c:v>0.1518046855926514</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.1046154946088791</c:v>
+                  <c:v>0.14108906686306</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.1016602516174316</c:v>
+                  <c:v>0.1116210967302322</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.1004781574010849</c:v>
+                  <c:v>0.1107281297445297</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.09929606318473816</c:v>
+                  <c:v>0.1098351553082466</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.09693186730146408</c:v>
+                  <c:v>0.1071562543511391</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.08747509866952896</c:v>
+                  <c:v>0.1071562543511391</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.08156462013721466</c:v>
+                  <c:v>0.1035843789577484</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.07801833748817444</c:v>
+                  <c:v>0.08661796897649765</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.07328995317220688</c:v>
+                  <c:v>0.08393906056880951</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.06856156885623932</c:v>
+                  <c:v>0.08036718517541885</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.06856156885623932</c:v>
+                  <c:v>0.07902773469686508</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.06619737297296524</c:v>
+                  <c:v>0.0767953172326088</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.06619737297296524</c:v>
+                  <c:v>0.07500937581062317</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.06619737297296524</c:v>
+                  <c:v>0.07322344183921814</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.0591048002243042</c:v>
+                  <c:v>0.07143750041723251</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.05555851012468338</c:v>
+                  <c:v>0.07054453343153</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.05083012580871582</c:v>
+                  <c:v>0.06965156644582748</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.04964803159236908</c:v>
+                  <c:v>0.06607969105243683</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.04610174149274826</c:v>
+                  <c:v>0.06161484494805336</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.04610174149274826</c:v>
+                  <c:v>0.05982890725135803</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.04373754933476448</c:v>
+                  <c:v>0.05536406487226486</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.04255545511841774</c:v>
+                  <c:v>0.05179218947887421</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.03782707080245018</c:v>
+                  <c:v>0.05179218947887421</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.03782707080245018</c:v>
+                  <c:v>0.05000625178217888</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.03664497658610344</c:v>
+                  <c:v>0.05000625178217888</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.03309868648648262</c:v>
+                  <c:v>0.0446484386920929</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.03309868648648262</c:v>
+                  <c:v>0.04196953028440476</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.03073449619114399</c:v>
+                  <c:v>0.04196953028440476</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.02837030403316021</c:v>
+                  <c:v>0.0383976586163044</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.02718820795416832</c:v>
+                  <c:v>0.03750468790531158</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.02600611187517643</c:v>
+                  <c:v>0.03482578322291374</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.01654934324324131</c:v>
+                  <c:v>0.03482578322291374</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.015367248095572</c:v>
+                  <c:v>0.03303984552621841</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.015367248095572</c:v>
+                  <c:v>0.0321468748152256</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.015367248095572</c:v>
+                  <c:v>0.03080742247402668</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.01063886377960444</c:v>
+                  <c:v>0.03036093711853027</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.009456767700612545</c:v>
+                  <c:v>0.0285750012844801</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.009456767700612545</c:v>
+                  <c:v>0.0285750012844801</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.008274671621620655</c:v>
+                  <c:v>0.02768203243613243</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.007092576008290052</c:v>
+                  <c:v>0.02500312589108944</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.007092576008290052</c:v>
+                  <c:v>0.02500312589108944</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.005910479929298163</c:v>
+                  <c:v>0.02321718819439411</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.005910479929298163</c:v>
+                  <c:v>0.02143125049769878</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.004728383850306273</c:v>
+                  <c:v>0.02053828164935112</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.004728383850306273</c:v>
+                  <c:v>0.02053828164935112</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.003546288004145026</c:v>
+                  <c:v>0.01964531280100346</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.003546288004145026</c:v>
+                  <c:v>0.01428750064224005</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.003546288004145026</c:v>
+                  <c:v>0.01250156294554472</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.002364191925153136</c:v>
+                  <c:v>0.01250156294554472</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.001182095962576568</c:v>
+                  <c:v>0.01250156294554472</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.001182095962576568</c:v>
+                  <c:v>0.01160859409719706</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.001182095962576568</c:v>
+                  <c:v>0.01160859409719706</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.001182095962576568</c:v>
+                  <c:v>0.01160859409719706</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.001182095962576568</c:v>
+                  <c:v>0.01071562524884939</c:v>
                 </c:pt>
                 <c:pt idx="145">
+                  <c:v>0.01071562524884939</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.0080367187038064</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.007143750321120024</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.007143750321120024</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.007143750321120024</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.007143750321120024</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.00625078147277236</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.005357812624424696</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.005357812624424696</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.005357812624424696</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.004464843776077032</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.004464843776077032</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.003571875160560012</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.003571875160560012</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.003571875160560012</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.003571875160560012</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.002678906312212348</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.002678906312212348</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.001785937580280006</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.000892968790140003</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.000892968790140003</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.000892968790140003</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.000892968790140003</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.000892968790140003</c:v>
+                </c:pt>
+                <c:pt idx="169">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1900,8 +2158,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H148" totalsRowCount="1">
-  <autoFilter ref="A2:H147"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H172" totalsRowCount="1">
+  <autoFilter ref="A2:H171"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1917,8 +2175,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H148" totalsRowCount="1">
-  <autoFilter ref="A2:H147"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H172" totalsRowCount="1">
+  <autoFilter ref="A2:H171"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -2218,7 +2476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2231,28 +2489,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="E2" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="F2" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="G2" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="H2" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2260,7 +2518,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>54.89635467529297</v>
+        <v>54.89880752563477</v>
       </c>
       <c r="C3" s="1">
         <v>24576</v>
@@ -2286,7 +2544,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>22.90922164916992</v>
+        <v>22.91024398803711</v>
       </c>
       <c r="C4" s="1">
         <v>10256</v>
@@ -2312,7 +2570,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>7.391440391540527</v>
+        <v>7.391770362854004</v>
       </c>
       <c r="C5" s="1">
         <v>3309</v>
@@ -2338,16 +2596,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>7.150196552276611</v>
+        <v>7.152750015258789</v>
       </c>
       <c r="C6" s="1">
-        <v>3201</v>
+        <v>3202</v>
       </c>
       <c r="D6" s="1">
-        <v>750</v>
+        <v>614</v>
       </c>
       <c r="E6" s="1">
-        <v>750</v>
+        <v>614</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -2356,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>3201</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2364,16 +2622,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>2.287348031997681</v>
+        <v>1.233078718185425</v>
       </c>
       <c r="C7" s="1">
-        <v>1024</v>
+        <v>552</v>
       </c>
       <c r="D7" s="1">
-        <v>164</v>
+        <v>654</v>
       </c>
       <c r="E7" s="1">
-        <v>164</v>
+        <v>654</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -2382,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>1024</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2390,7 +2648,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>1.188348770141602</v>
+        <v>1.188401937484741</v>
       </c>
       <c r="C8" s="1">
         <v>532</v>
@@ -2416,16 +2674,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.8041458129882813</v>
+        <v>1.179466605186462</v>
       </c>
       <c r="C9" s="1">
-        <v>360</v>
+        <v>528</v>
       </c>
       <c r="D9" s="1">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="E9" s="1">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -2434,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>360</v>
+        <v>528</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2442,7 +2700,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.7505360841751099</v>
+        <v>0.7505696415901184</v>
       </c>
       <c r="C10" s="1">
         <v>336</v>
@@ -2468,7 +2726,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.5897069573402405</v>
+        <v>0.5897333025932312</v>
       </c>
       <c r="C11" s="1">
         <v>264</v>
@@ -2494,16 +2752,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.4020729064941406</v>
+        <v>0.5718625783920288</v>
       </c>
       <c r="C12" s="1">
-        <v>180</v>
+        <v>256</v>
       </c>
       <c r="D12" s="1">
-        <v>232</v>
+        <v>164</v>
       </c>
       <c r="E12" s="1">
-        <v>232</v>
+        <v>164</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -2512,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>180</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2520,25 +2778,25 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.2412437498569489</v>
+        <v>0.4020908772945404</v>
       </c>
       <c r="C13" s="1">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="D13" s="1">
-        <v>8374</v>
+        <v>232</v>
       </c>
       <c r="E13" s="1">
-        <v>8352</v>
+        <v>232</v>
       </c>
       <c r="F13" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>108</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2546,25 +2804,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.2144388854503632</v>
+        <v>0.241254523396492</v>
       </c>
       <c r="C14" s="1">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D14" s="1">
-        <v>1148</v>
+        <v>8374</v>
       </c>
       <c r="E14" s="1">
-        <v>1148</v>
+        <v>8352</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2572,22 +2830,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.2144388854503632</v>
+        <v>0.2233838140964508</v>
       </c>
       <c r="C15" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D15" s="1">
-        <v>8</v>
+        <v>1982</v>
       </c>
       <c r="E15" s="1">
-        <v>8</v>
+        <v>1706</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H15" s="1">
         <v>96</v>
@@ -2598,16 +2856,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.1608291566371918</v>
+        <v>0.2144484668970108</v>
       </c>
       <c r="C16" s="1">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D16" s="1">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="E16" s="1">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -2616,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>72</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2624,25 +2882,25 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.1608291566371918</v>
+        <v>0.1608363538980484</v>
       </c>
       <c r="C17" s="1">
         <v>72</v>
       </c>
       <c r="D17" s="1">
-        <v>1879</v>
+        <v>116</v>
       </c>
       <c r="E17" s="1">
-        <v>714</v>
+        <v>116</v>
       </c>
       <c r="F17" s="1">
-        <v>1093</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
         <v>72</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2650,25 +2908,25 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.07147962599992752</v>
+        <v>0.1608363538980484</v>
       </c>
       <c r="C18" s="1">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="D18" s="1">
-        <v>4484</v>
+        <v>1875</v>
       </c>
       <c r="E18" s="1">
-        <v>4484</v>
+        <v>714</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>1089</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H18" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2676,25 +2934,25 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.06254467368125916</v>
+        <v>0.0714828222990036</v>
       </c>
       <c r="C19" s="1">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D19" s="1">
-        <v>1836</v>
+        <v>4484</v>
       </c>
       <c r="E19" s="1">
-        <v>1808</v>
+        <v>4484</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2702,19 +2960,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.06254467368125916</v>
+        <v>0.062547467648983</v>
       </c>
       <c r="C20" s="1">
         <v>28</v>
       </c>
       <c r="D20" s="1">
-        <v>4023</v>
+        <v>1836</v>
       </c>
       <c r="E20" s="1">
-        <v>3942</v>
+        <v>1808</v>
       </c>
       <c r="F20" s="1">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
         <v>28</v>
@@ -2728,25 +2986,25 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.04914224520325661</v>
+        <v>0.062547467648983</v>
       </c>
       <c r="C21" s="1">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D21" s="1">
-        <v>2438</v>
+        <v>4023</v>
       </c>
       <c r="E21" s="1">
-        <v>2438</v>
+        <v>3942</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H21" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2754,16 +3012,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.04467476904392242</v>
+        <v>0.0491444393992424</v>
       </c>
       <c r="C22" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D22" s="1">
-        <v>506</v>
+        <v>2438</v>
       </c>
       <c r="E22" s="1">
-        <v>506</v>
+        <v>2438</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2772,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2780,25 +3038,25 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.0268048606812954</v>
+        <v>0.0446767620742321</v>
       </c>
       <c r="C23" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D23" s="1">
-        <v>188</v>
+        <v>506</v>
       </c>
       <c r="E23" s="1">
-        <v>180</v>
+        <v>506</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2806,25 +3064,25 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.0268048606812954</v>
+        <v>0.0357414111495018</v>
       </c>
       <c r="C24" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D24" s="1">
-        <v>406</v>
+        <v>459</v>
       </c>
       <c r="E24" s="1">
-        <v>350</v>
+        <v>444</v>
       </c>
       <c r="F24" s="1">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H24" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2832,25 +3090,25 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.0268048606812954</v>
+        <v>0.02680605836212635</v>
       </c>
       <c r="C25" s="1">
         <v>12</v>
       </c>
       <c r="D25" s="1">
-        <v>2748</v>
+        <v>188</v>
       </c>
       <c r="E25" s="1">
-        <v>2748</v>
+        <v>180</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H25" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -2858,19 +3116,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.0268048606812954</v>
+        <v>0.02680605836212635</v>
       </c>
       <c r="C26" s="1">
         <v>12</v>
       </c>
       <c r="D26" s="1">
-        <v>938</v>
+        <v>406</v>
       </c>
       <c r="E26" s="1">
-        <v>938</v>
+        <v>350</v>
       </c>
       <c r="F26" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
@@ -2884,25 +3142,25 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.0268048606812954</v>
+        <v>0.02680605836212635</v>
       </c>
       <c r="C27" s="1">
         <v>12</v>
       </c>
       <c r="D27" s="1">
-        <v>1504</v>
+        <v>2748</v>
       </c>
       <c r="E27" s="1">
-        <v>1500</v>
+        <v>2748</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -2910,16 +3168,16 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.0268048606812954</v>
+        <v>0.02680605836212635</v>
       </c>
       <c r="C28" s="1">
         <v>12</v>
       </c>
       <c r="D28" s="1">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="E28" s="1">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2936,25 +3194,25 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02010364457964897</v>
+        <v>0.02680605836212635</v>
       </c>
       <c r="C29" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D29" s="1">
-        <v>2556</v>
+        <v>1504</v>
       </c>
       <c r="E29" s="1">
-        <v>2524</v>
+        <v>1500</v>
       </c>
       <c r="F29" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
         <v>4</v>
       </c>
       <c r="H29" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -2962,25 +3220,25 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.01786990649998188</v>
+        <v>0.02680605836212635</v>
       </c>
       <c r="C30" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D30" s="1">
-        <v>168</v>
+        <v>940</v>
       </c>
       <c r="E30" s="1">
-        <v>140</v>
+        <v>940</v>
       </c>
       <c r="F30" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2988,25 +3246,25 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.01786990649998188</v>
+        <v>0.02010454423725605</v>
       </c>
       <c r="C31" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" s="1">
-        <v>342</v>
+        <v>2556</v>
       </c>
       <c r="E31" s="1">
-        <v>342</v>
+        <v>2524</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H31" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3014,19 +3272,19 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.01786990649998188</v>
+        <v>0.0178707055747509</v>
       </c>
       <c r="C32" s="1">
         <v>8</v>
       </c>
       <c r="D32" s="1">
-        <v>48</v>
+        <v>168</v>
       </c>
       <c r="E32" s="1">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -3040,19 +3298,19 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.01786990649998188</v>
+        <v>0.0178707055747509</v>
       </c>
       <c r="C33" s="1">
         <v>8</v>
       </c>
       <c r="D33" s="1">
-        <v>13633</v>
+        <v>342</v>
       </c>
       <c r="E33" s="1">
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="F33" s="1">
-        <v>13633</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
@@ -3066,25 +3324,25 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.0134024303406477</v>
+        <v>0.0178707055747509</v>
       </c>
       <c r="C34" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D34" s="1">
-        <v>1183</v>
+        <v>48</v>
       </c>
       <c r="E34" s="1">
-        <v>1068</v>
+        <v>48</v>
       </c>
       <c r="F34" s="1">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -3092,25 +3350,25 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.01116869226098061</v>
+        <v>0.0178707055747509</v>
       </c>
       <c r="C35" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D35" s="1">
-        <v>5342</v>
+        <v>13633</v>
       </c>
       <c r="E35" s="1">
-        <v>5342</v>
+        <v>0</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>13633</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -3118,25 +3376,25 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.01116869226098061</v>
+        <v>0.0178707055747509</v>
       </c>
       <c r="C36" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D36" s="1">
-        <v>3234</v>
+        <v>36243</v>
       </c>
       <c r="E36" s="1">
-        <v>3206</v>
+        <v>0</v>
       </c>
       <c r="F36" s="1">
-        <v>28</v>
+        <v>36243</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -3144,25 +3402,25 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.00893495324999094</v>
+        <v>0.0178707055747509</v>
       </c>
       <c r="C37" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D37" s="1">
-        <v>44</v>
+        <v>10824</v>
       </c>
       <c r="E37" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F37" s="1">
-        <v>24</v>
+        <v>10824</v>
       </c>
       <c r="G37" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -3170,22 +3428,22 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.00893495324999094</v>
+        <v>0.01340302918106318</v>
       </c>
       <c r="C38" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D38" s="1">
-        <v>3944</v>
+        <v>1183</v>
       </c>
       <c r="E38" s="1">
-        <v>3916</v>
+        <v>1068</v>
       </c>
       <c r="F38" s="1">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38" s="1">
         <v>4</v>
@@ -3196,25 +3454,25 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.00893495324999094</v>
+        <v>0.01116919051855803</v>
       </c>
       <c r="C39" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" s="1">
-        <v>896</v>
+        <v>5342</v>
       </c>
       <c r="E39" s="1">
-        <v>868</v>
+        <v>5342</v>
       </c>
       <c r="F39" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G39" s="1">
         <v>0</v>
       </c>
       <c r="H39" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -3222,25 +3480,25 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.00893495324999094</v>
+        <v>0.01116919051855803</v>
       </c>
       <c r="C40" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D40" s="1">
-        <v>542</v>
+        <v>3348</v>
       </c>
       <c r="E40" s="1">
-        <v>542</v>
+        <v>3320</v>
       </c>
       <c r="F40" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -3248,25 +3506,25 @@
         <v>39</v>
       </c>
       <c r="B41" s="2">
-        <v>0.00893495324999094</v>
+        <v>0.00893535278737545</v>
       </c>
       <c r="C41" s="1">
         <v>4</v>
       </c>
       <c r="D41" s="1">
-        <v>828</v>
+        <v>16</v>
       </c>
       <c r="E41" s="1">
-        <v>828</v>
+        <v>12</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H41" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -3274,19 +3532,19 @@
         <v>40</v>
       </c>
       <c r="B42" s="2">
-        <v>0.00893495324999094</v>
+        <v>0.00893535278737545</v>
       </c>
       <c r="C42" s="1">
         <v>4</v>
       </c>
       <c r="D42" s="1">
-        <v>642</v>
+        <v>582</v>
       </c>
       <c r="E42" s="1">
-        <v>642</v>
+        <v>580</v>
       </c>
       <c r="F42" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
@@ -3300,25 +3558,25 @@
         <v>41</v>
       </c>
       <c r="B43" s="2">
-        <v>0.00446747662499547</v>
+        <v>0.00893535278737545</v>
       </c>
       <c r="C43" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D43" s="1">
-        <v>148</v>
+        <v>44</v>
       </c>
       <c r="E43" s="1">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="F43" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H43" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -3326,56 +3584,238 @@
         <v>42</v>
       </c>
       <c r="B44" s="2">
-        <v>0.002233738312497735</v>
+        <v>0.00893535278737545</v>
       </c>
       <c r="C44" s="1">
+        <v>4</v>
+      </c>
+      <c r="D44" s="1">
+        <v>3944</v>
+      </c>
+      <c r="E44" s="1">
+        <v>3916</v>
+      </c>
+      <c r="F44" s="1">
+        <v>28</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0.00893535278737545</v>
+      </c>
+      <c r="C45" s="1">
+        <v>4</v>
+      </c>
+      <c r="D45" s="1">
+        <v>896</v>
+      </c>
+      <c r="E45" s="1">
+        <v>868</v>
+      </c>
+      <c r="F45" s="1">
+        <v>28</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="2">
+        <v>0.00893535278737545</v>
+      </c>
+      <c r="C46" s="1">
+        <v>4</v>
+      </c>
+      <c r="D46" s="1">
+        <v>542</v>
+      </c>
+      <c r="E46" s="1">
+        <v>542</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="2">
+        <v>0.00893535278737545</v>
+      </c>
+      <c r="C47" s="1">
+        <v>4</v>
+      </c>
+      <c r="D47" s="1">
+        <v>828</v>
+      </c>
+      <c r="E47" s="1">
+        <v>828</v>
+      </c>
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="2">
+        <v>0.00893535278737545</v>
+      </c>
+      <c r="C48" s="1">
+        <v>4</v>
+      </c>
+      <c r="D48" s="1">
+        <v>642</v>
+      </c>
+      <c r="E48" s="1">
+        <v>642</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0.004467676393687725</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2</v>
+      </c>
+      <c r="D49" s="1">
+        <v>148</v>
+      </c>
+      <c r="E49" s="1">
+        <v>120</v>
+      </c>
+      <c r="F49" s="1">
+        <v>28</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="2">
+        <v>0.002233838196843863</v>
+      </c>
+      <c r="C50" s="1">
         <v>1</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D50" s="1">
+        <v>69</v>
+      </c>
+      <c r="E50" s="1">
+        <v>68</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2">
+        <v>0.002233838196843863</v>
+      </c>
+      <c r="C51" s="1">
+        <v>1</v>
+      </c>
+      <c r="D51" s="1">
         <v>3589</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E51" s="1">
         <v>3588</v>
       </c>
-      <c r="F44" s="1">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1">
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
         <v>1</v>
       </c>
-      <c r="H44" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8">
-      <c r="A148" t="s">
-        <v>148</v>
-      </c>
-      <c r="B148">
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" t="s">
+        <v>172</v>
+      </c>
+      <c r="B172">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C148">
+      <c r="C172">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D148">
+      <c r="D172">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E148">
+      <c r="E172">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F148">
+      <c r="F172">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G148">
+      <c r="G172">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H148">
+      <c r="H172">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -3391,7 +3831,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -3404,39 +3844,39 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="F2" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="G2" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="H2" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2">
-        <v>8.057757377624512</v>
+        <v>16.18193435668945</v>
       </c>
       <c r="C3" s="1">
-        <v>13633</v>
+        <v>36243</v>
       </c>
       <c r="D3" s="1">
         <v>8</v>
@@ -3445,7 +3885,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>13633</v>
+        <v>36243</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -3456,123 +3896,123 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2">
-        <v>4.949435710906982</v>
+        <v>6.086921691894531</v>
       </c>
       <c r="C4" s="1">
-        <v>8374</v>
+        <v>13633</v>
       </c>
       <c r="D4" s="1">
-        <v>108</v>
+        <v>8</v>
       </c>
       <c r="E4" s="1">
-        <v>8352</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>22</v>
+        <v>13633</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>108</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2">
-        <v>4.196440696716309</v>
+        <v>4.832746982574463</v>
       </c>
       <c r="C5" s="1">
-        <v>7100</v>
+        <v>10824</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1">
-        <v>7072</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>28</v>
+        <v>10824</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2">
-        <v>3.917466163635254</v>
+        <v>3.738860130310059</v>
       </c>
       <c r="C6" s="1">
-        <v>6628</v>
+        <v>8374</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="E6" s="1">
-        <v>6628</v>
+        <v>8352</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2">
-        <v>3.157378435134888</v>
+        <v>3.170039176940918</v>
       </c>
       <c r="C7" s="1">
-        <v>5342</v>
+        <v>7100</v>
       </c>
       <c r="D7" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>5342</v>
+        <v>7072</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2">
-        <v>2.650259256362915</v>
+        <v>2.959298372268677</v>
       </c>
       <c r="C8" s="1">
-        <v>4484</v>
+        <v>6628</v>
       </c>
       <c r="D8" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>4484</v>
+        <v>6628</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -3581,50 +4021,50 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B9" s="2">
-        <v>2.494222402572632</v>
+        <v>2.385119676589966</v>
       </c>
       <c r="C9" s="1">
-        <v>4220</v>
+        <v>5342</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1">
-        <v>4192</v>
+        <v>5342</v>
       </c>
       <c r="F9" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2">
-        <v>2.483583688735962</v>
+        <v>2.002035856246948</v>
       </c>
       <c r="C10" s="1">
-        <v>4202</v>
+        <v>4484</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E10" s="1">
-        <v>4202</v>
+        <v>4484</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -3633,27 +4073,27 @@
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B11" s="2">
-        <v>2.449302911758423</v>
+        <v>1.884164094924927</v>
       </c>
       <c r="C11" s="1">
-        <v>4144</v>
+        <v>4220</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>4144</v>
+        <v>4192</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -3664,25 +4104,25 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2">
-        <v>2.377786159515381</v>
+        <v>1.876127362251282</v>
       </c>
       <c r="C12" s="1">
-        <v>4023</v>
+        <v>4202</v>
       </c>
       <c r="D12" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>3942</v>
+        <v>4202</v>
       </c>
       <c r="F12" s="1">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
         <v>0</v>
@@ -3690,51 +4130,51 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2">
-        <v>2.331093311309815</v>
+        <v>1.850231289863586</v>
       </c>
       <c r="C13" s="1">
-        <v>3944</v>
+        <v>4144</v>
       </c>
       <c r="D13" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>3916</v>
+        <v>4144</v>
       </c>
       <c r="F13" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2">
-        <v>2.192788124084473</v>
+        <v>1.796206712722778</v>
       </c>
       <c r="C14" s="1">
-        <v>3710</v>
+        <v>4023</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E14" s="1">
-        <v>3698</v>
+        <v>3942</v>
       </c>
       <c r="F14" s="1">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H14" s="1">
         <v>0</v>
@@ -3745,45 +4185,45 @@
         <v>42</v>
       </c>
       <c r="B15" s="2">
-        <v>2.121271133422852</v>
+        <v>1.760934352874756</v>
       </c>
       <c r="C15" s="1">
-        <v>3589</v>
+        <v>3944</v>
       </c>
       <c r="D15" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" s="1">
-        <v>3588</v>
+        <v>3916</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B16" s="2">
-        <v>1.94218373298645</v>
+        <v>1.65645706653595</v>
       </c>
       <c r="C16" s="1">
-        <v>3286</v>
+        <v>3710</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>3230</v>
+        <v>3698</v>
       </c>
       <c r="F16" s="1">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -3794,74 +4234,74 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2">
-        <v>1.911449193954468</v>
+        <v>1.602432489395142</v>
       </c>
       <c r="C17" s="1">
-        <v>3234</v>
+        <v>3589</v>
       </c>
       <c r="D17" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17" s="1">
-        <v>3206</v>
+        <v>3588</v>
       </c>
       <c r="F17" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2">
-        <v>1.906720757484436</v>
+        <v>1.494829654693604</v>
       </c>
       <c r="C18" s="1">
-        <v>3226</v>
+        <v>3348</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E18" s="1">
-        <v>3226</v>
+        <v>3320</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B19" s="2">
-        <v>1.854708552360535</v>
+        <v>1.467147707939148</v>
       </c>
       <c r="C19" s="1">
-        <v>3138</v>
+        <v>3286</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>3110</v>
+        <v>3230</v>
       </c>
       <c r="F19" s="1">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -3872,19 +4312,19 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2">
-        <v>1.71994960308075</v>
+        <v>1.440358638763428</v>
       </c>
       <c r="C20" s="1">
-        <v>2910</v>
+        <v>3226</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>2910</v>
+        <v>3226</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -3898,19 +4338,19 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B21" s="2">
-        <v>1.679758429527283</v>
+        <v>1.401067972183228</v>
       </c>
       <c r="C21" s="1">
-        <v>2842</v>
+        <v>3138</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>2814</v>
+        <v>3110</v>
       </c>
       <c r="F21" s="1">
         <v>28</v>
@@ -3924,19 +4364,19 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="B22" s="2">
-        <v>1.624199867248535</v>
+        <v>1.299269556999207</v>
       </c>
       <c r="C22" s="1">
-        <v>2748</v>
+        <v>2910</v>
       </c>
       <c r="D22" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>2748</v>
+        <v>2910</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -3945,27 +4385,27 @@
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B23" s="2">
-        <v>1.567459225654602</v>
+        <v>1.268908619880676</v>
       </c>
       <c r="C23" s="1">
-        <v>2652</v>
+        <v>2842</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>2596</v>
+        <v>2814</v>
       </c>
       <c r="F23" s="1">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
@@ -3976,123 +4416,123 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B24" s="2">
-        <v>1.510718703269959</v>
+        <v>1.226939082145691</v>
       </c>
       <c r="C24" s="1">
-        <v>2556</v>
+        <v>2748</v>
       </c>
       <c r="D24" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E24" s="1">
-        <v>2524</v>
+        <v>2748</v>
       </c>
       <c r="F24" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="B25" s="2">
-        <v>1.440974950790405</v>
+        <v>1.184076547622681</v>
       </c>
       <c r="C25" s="1">
-        <v>2438</v>
+        <v>2652</v>
       </c>
       <c r="D25" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>2438</v>
+        <v>2596</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B26" s="2">
-        <v>1.262478470802307</v>
+        <v>1.14121413230896</v>
       </c>
       <c r="C26" s="1">
-        <v>2136</v>
+        <v>2556</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E26" s="1">
-        <v>2108</v>
+        <v>2524</v>
       </c>
       <c r="F26" s="1">
         <v>28</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="B27" s="2">
-        <v>1.260114312171936</v>
+        <v>1.088528871536255</v>
       </c>
       <c r="C27" s="1">
-        <v>2132</v>
+        <v>2438</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E27" s="1">
-        <v>2104</v>
+        <v>2438</v>
       </c>
       <c r="F27" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B28" s="2">
-        <v>1.211648344993591</v>
+        <v>1.05906093120575</v>
       </c>
       <c r="C28" s="1">
-        <v>2050</v>
+        <v>2372</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>2050</v>
+        <v>2372</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -4106,19 +4546,19 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B29" s="2">
-        <v>1.208102107048035</v>
+        <v>0.9536906480789185</v>
       </c>
       <c r="C29" s="1">
-        <v>2044</v>
+        <v>2136</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>2016</v>
+        <v>2108</v>
       </c>
       <c r="F29" s="1">
         <v>28</v>
@@ -4132,22 +4572,22 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B30" s="2">
-        <v>1.195098996162415</v>
+        <v>0.9519047141075134</v>
       </c>
       <c r="C30" s="1">
-        <v>2022</v>
+        <v>2132</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>2022</v>
+        <v>2104</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
@@ -4158,22 +4598,22 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B31" s="2">
-        <v>1.182096004486084</v>
+        <v>0.9152929782867432</v>
       </c>
       <c r="C31" s="1">
-        <v>2000</v>
+        <v>2050</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>1972</v>
+        <v>2050</v>
       </c>
       <c r="F31" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -4184,22 +4624,22 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B32" s="2">
-        <v>1.164364576339722</v>
+        <v>0.9126140475273132</v>
       </c>
       <c r="C32" s="1">
-        <v>1970</v>
+        <v>2044</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>1966</v>
+        <v>2016</v>
       </c>
       <c r="F32" s="1">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -4210,19 +4650,19 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B33" s="2">
-        <v>1.130083799362183</v>
+        <v>0.902791440486908</v>
       </c>
       <c r="C33" s="1">
-        <v>1912</v>
+        <v>2022</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>1912</v>
+        <v>2022</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -4236,25 +4676,25 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B34" s="2">
-        <v>1.110579133033752</v>
+        <v>0.8929687738418579</v>
       </c>
       <c r="C34" s="1">
-        <v>1879</v>
+        <v>2000</v>
       </c>
       <c r="D34" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>714</v>
+        <v>1972</v>
       </c>
       <c r="F34" s="1">
-        <v>1093</v>
+        <v>28</v>
       </c>
       <c r="G34" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -4262,48 +4702,48 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B35" s="2">
-        <v>1.085164070129395</v>
+        <v>0.8849320411682129</v>
       </c>
       <c r="C35" s="1">
-        <v>1836</v>
+        <v>1982</v>
       </c>
       <c r="D35" s="1">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="E35" s="1">
-        <v>1808</v>
+        <v>1706</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="G35" s="1">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B36" s="2">
-        <v>1.01305627822876</v>
+        <v>0.8795742392539978</v>
       </c>
       <c r="C36" s="1">
-        <v>1714</v>
+        <v>1970</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>1714</v>
+        <v>1966</v>
       </c>
       <c r="F36" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
@@ -4314,19 +4754,19 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B37" s="2">
-        <v>0.9870501160621643</v>
+        <v>0.8536781668663025</v>
       </c>
       <c r="C37" s="1">
-        <v>1670</v>
+        <v>1912</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>1670</v>
+        <v>1912</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -4340,51 +4780,51 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B38" s="2">
-        <v>0.8889361619949341</v>
+        <v>0.837158203125</v>
       </c>
       <c r="C38" s="1">
-        <v>1504</v>
+        <v>1875</v>
       </c>
       <c r="D38" s="1">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="E38" s="1">
-        <v>1500</v>
+        <v>714</v>
       </c>
       <c r="F38" s="1">
-        <v>0</v>
+        <v>1089</v>
       </c>
       <c r="G38" s="1">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="H38" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="B39" s="2">
-        <v>0.8499270081520081</v>
+        <v>0.8197453022003174</v>
       </c>
       <c r="C39" s="1">
-        <v>1438</v>
+        <v>1836</v>
       </c>
       <c r="D39" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E39" s="1">
-        <v>1438</v>
+        <v>1808</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -4392,48 +4832,48 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="B40" s="2">
-        <v>0.7813654541969299</v>
+        <v>0.7652742266654968</v>
       </c>
       <c r="C40" s="1">
-        <v>1322</v>
+        <v>1714</v>
       </c>
       <c r="D40" s="1">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>1044</v>
+        <v>1714</v>
       </c>
       <c r="F40" s="1">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B41" s="2">
-        <v>0.776637077331543</v>
+        <v>0.7456288933753967</v>
       </c>
       <c r="C41" s="1">
-        <v>1314</v>
+        <v>1670</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>1050</v>
+        <v>1670</v>
       </c>
       <c r="F41" s="1">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1">
         <v>0</v>
@@ -4444,45 +4884,45 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="B42" s="2">
-        <v>0.7459025382995606</v>
+        <v>0.6715124845504761</v>
       </c>
       <c r="C42" s="1">
-        <v>1262</v>
+        <v>1504</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E42" s="1">
-        <v>1262</v>
+        <v>1500</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H42" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B43" s="2">
-        <v>0.7364457845687866</v>
+        <v>0.6420445442199707</v>
       </c>
       <c r="C43" s="1">
-        <v>1246</v>
+        <v>1438</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>1246</v>
+        <v>1438</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -4496,48 +4936,48 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B44" s="2">
-        <v>0.6992097496986389</v>
+        <v>0.5902523398399353</v>
       </c>
       <c r="C44" s="1">
-        <v>1183</v>
+        <v>1322</v>
       </c>
       <c r="D44" s="1">
-        <v>6</v>
+        <v>264</v>
       </c>
       <c r="E44" s="1">
-        <v>1068</v>
+        <v>1044</v>
       </c>
       <c r="F44" s="1">
-        <v>113</v>
+        <v>278</v>
       </c>
       <c r="G44" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" s="1">
-        <v>4</v>
+        <v>264</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B45" s="2">
-        <v>0.6915261745452881</v>
+        <v>0.5866804718971252</v>
       </c>
       <c r="C45" s="1">
-        <v>1170</v>
+        <v>1314</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>1170</v>
+        <v>1050</v>
       </c>
       <c r="F45" s="1">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
@@ -4548,19 +4988,19 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B46" s="2">
-        <v>0.6867977380752564</v>
+        <v>0.5634632706642151</v>
       </c>
       <c r="C46" s="1">
-        <v>1162</v>
+        <v>1262</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>1162</v>
+        <v>1262</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -4574,19 +5014,19 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="B47" s="2">
-        <v>0.678523063659668</v>
+        <v>0.556319534778595</v>
       </c>
       <c r="C47" s="1">
-        <v>1148</v>
+        <v>1246</v>
       </c>
       <c r="D47" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>1148</v>
+        <v>1246</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -4595,24 +5035,24 @@
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B48" s="2">
-        <v>0.6501528024673462</v>
+        <v>0.5429250001907349</v>
       </c>
       <c r="C48" s="1">
-        <v>1100</v>
+        <v>1216</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>1048</v>
+        <v>1164</v>
       </c>
       <c r="F48" s="1">
         <v>52</v>
@@ -4626,48 +5066,48 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="B49" s="2">
-        <v>0.5934121608734131</v>
+        <v>0.5281910300254822</v>
       </c>
       <c r="C49" s="1">
-        <v>1004</v>
+        <v>1183</v>
       </c>
       <c r="D49" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E49" s="1">
-        <v>1004</v>
+        <v>1068</v>
       </c>
       <c r="F49" s="1">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="G49" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B50" s="2">
-        <v>0.5857285261154175</v>
+        <v>0.5223867297172546</v>
       </c>
       <c r="C50" s="1">
-        <v>991</v>
+        <v>1170</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>348</v>
+        <v>1170</v>
       </c>
       <c r="F50" s="1">
-        <v>643</v>
+        <v>0</v>
       </c>
       <c r="G50" s="1">
         <v>0</v>
@@ -4678,19 +5118,19 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B51" s="2">
-        <v>0.5815912485122681</v>
+        <v>0.448270320892334</v>
       </c>
       <c r="C51" s="1">
-        <v>984</v>
+        <v>1004</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>984</v>
+        <v>1004</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -4704,71 +5144,71 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="B52" s="2">
-        <v>0.563859760761261</v>
+        <v>0.4446984529495239</v>
       </c>
       <c r="C52" s="1">
-        <v>954</v>
+        <v>996</v>
       </c>
       <c r="D52" s="1">
-        <v>10256</v>
+        <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>950</v>
+        <v>996</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>10252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="B53" s="2">
-        <v>0.5555850863456726</v>
+        <v>0.4424660205841065</v>
       </c>
       <c r="C53" s="1">
-        <v>940</v>
+        <v>991</v>
       </c>
       <c r="D53" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>940</v>
+        <v>348</v>
       </c>
       <c r="F53" s="1">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="G53" s="1">
         <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="B54" s="2">
-        <v>0.5544030070304871</v>
+        <v>0.4393406212329865</v>
       </c>
       <c r="C54" s="1">
-        <v>938</v>
+        <v>984</v>
       </c>
       <c r="D54" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>938</v>
+        <v>984</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -4777,53 +5217,53 @@
         <v>0</v>
       </c>
       <c r="H54" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B55" s="2">
-        <v>0.5295789837837219</v>
+        <v>0.4259460866451263</v>
       </c>
       <c r="C55" s="1">
-        <v>896</v>
+        <v>954</v>
       </c>
       <c r="D55" s="1">
+        <v>10256</v>
+      </c>
+      <c r="E55" s="1">
+        <v>950</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
         <v>4</v>
       </c>
-      <c r="E55" s="1">
-        <v>868</v>
-      </c>
-      <c r="F55" s="1">
-        <v>28</v>
-      </c>
-      <c r="G55" s="1">
-        <v>0</v>
-      </c>
       <c r="H55" s="1">
-        <v>4</v>
+        <v>10252</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B56" s="2">
-        <v>0.5236685276031494</v>
+        <v>0.4241601526737213</v>
       </c>
       <c r="C56" s="1">
-        <v>886</v>
+        <v>950</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>886</v>
+        <v>916</v>
       </c>
       <c r="F56" s="1">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G56" s="1">
         <v>0</v>
@@ -4834,74 +5274,74 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="B57" s="2">
-        <v>0.520122230052948</v>
+        <v>0.4196953177452087</v>
       </c>
       <c r="C57" s="1">
-        <v>880</v>
+        <v>940</v>
       </c>
       <c r="D57" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E57" s="1">
-        <v>852</v>
+        <v>940</v>
       </c>
       <c r="F57" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="B58" s="2">
-        <v>0.5165759325027466</v>
+        <v>0.4188023507595062</v>
       </c>
       <c r="C58" s="1">
-        <v>874</v>
+        <v>938</v>
       </c>
       <c r="D58" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E58" s="1">
-        <v>846</v>
+        <v>938</v>
       </c>
       <c r="F58" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G58" s="1">
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B59" s="2">
-        <v>0.489387720823288</v>
+        <v>0.400050014257431</v>
       </c>
       <c r="C59" s="1">
-        <v>828</v>
+        <v>896</v>
       </c>
       <c r="D59" s="1">
         <v>4</v>
       </c>
       <c r="E59" s="1">
-        <v>828</v>
+        <v>868</v>
       </c>
       <c r="F59" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G59" s="1">
         <v>0</v>
@@ -4912,22 +5352,22 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B60" s="2">
-        <v>0.4621995389461517</v>
+        <v>0.3955851495265961</v>
       </c>
       <c r="C60" s="1">
-        <v>782</v>
+        <v>886</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>402</v>
+        <v>886</v>
       </c>
       <c r="F60" s="1">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="G60" s="1">
         <v>0</v>
@@ -4938,22 +5378,22 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B61" s="2">
-        <v>0.4574711322784424</v>
+        <v>0.3929062485694885</v>
       </c>
       <c r="C61" s="1">
-        <v>774</v>
+        <v>880</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>766</v>
+        <v>852</v>
       </c>
       <c r="F61" s="1">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G61" s="1">
         <v>0</v>
@@ -4964,22 +5404,22 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B62" s="2">
-        <v>0.449196457862854</v>
+        <v>0.390227347612381</v>
       </c>
       <c r="C62" s="1">
-        <v>760</v>
+        <v>874</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>760</v>
+        <v>846</v>
       </c>
       <c r="F62" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
@@ -4990,19 +5430,19 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="2">
+        <v>0.3696890771389008</v>
+      </c>
+      <c r="C63" s="1">
+        <v>828</v>
+      </c>
+      <c r="D63" s="1">
         <v>4</v>
       </c>
-      <c r="B63" s="2">
-        <v>0.4432860016822815</v>
-      </c>
-      <c r="C63" s="1">
-        <v>750</v>
-      </c>
-      <c r="D63" s="1">
-        <v>3201</v>
-      </c>
       <c r="E63" s="1">
-        <v>750</v>
+        <v>828</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -5011,27 +5451,27 @@
         <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>3201</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B64" s="2">
-        <v>0.4385575950145721</v>
+        <v>0.3491507768630981</v>
       </c>
       <c r="C64" s="1">
-        <v>742</v>
+        <v>782</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>714</v>
+        <v>402</v>
       </c>
       <c r="F64" s="1">
-        <v>28</v>
+        <v>380</v>
       </c>
       <c r="G64" s="1">
         <v>0</v>
@@ -5042,22 +5482,22 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B65" s="2">
-        <v>0.4137336015701294</v>
+        <v>0.3455789089202881</v>
       </c>
       <c r="C65" s="1">
-        <v>700</v>
+        <v>774</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>700</v>
+        <v>766</v>
       </c>
       <c r="F65" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
@@ -5068,19 +5508,19 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B66" s="2">
-        <v>0.4078231155872345</v>
+        <v>0.3393281400203705</v>
       </c>
       <c r="C66" s="1">
-        <v>690</v>
+        <v>760</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>690</v>
+        <v>760</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -5094,48 +5534,48 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B67" s="2">
-        <v>0.3794527947902679</v>
+        <v>0.3312914073467255</v>
       </c>
       <c r="C67" s="1">
-        <v>642</v>
+        <v>742</v>
       </c>
       <c r="D67" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>642</v>
+        <v>714</v>
       </c>
       <c r="F67" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G67" s="1">
         <v>0</v>
       </c>
       <c r="H67" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B68" s="2">
-        <v>0.3629034757614136</v>
+        <v>0.3125390708446503</v>
       </c>
       <c r="C68" s="1">
-        <v>614</v>
+        <v>700</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>432</v>
+        <v>700</v>
       </c>
       <c r="F68" s="1">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="G68" s="1">
         <v>0</v>
@@ -5146,19 +5586,19 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B69" s="2">
-        <v>0.3593571782112122</v>
+        <v>0.3080742359161377</v>
       </c>
       <c r="C69" s="1">
-        <v>608</v>
+        <v>690</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>608</v>
+        <v>690</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -5172,22 +5612,22 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B70" s="2">
-        <v>0.3380794525146484</v>
+        <v>0.3009304702281952</v>
       </c>
       <c r="C70" s="1">
-        <v>572</v>
+        <v>674</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>404</v>
+        <v>674</v>
       </c>
       <c r="F70" s="1">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="G70" s="1">
         <v>0</v>
@@ -5198,19 +5638,19 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B71" s="2">
-        <v>0.3238942921161652</v>
+        <v>0.29200080037117</v>
       </c>
       <c r="C71" s="1">
-        <v>548</v>
+        <v>654</v>
       </c>
       <c r="D71" s="1">
-        <v>360</v>
+        <v>552</v>
       </c>
       <c r="E71" s="1">
-        <v>548</v>
+        <v>654</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -5219,50 +5659,50 @@
         <v>0</v>
       </c>
       <c r="H71" s="1">
-        <v>360</v>
+        <v>552</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="B72" s="2">
-        <v>0.3215301036834717</v>
+        <v>0.2866429686546326</v>
       </c>
       <c r="C72" s="1">
-        <v>544</v>
+        <v>642</v>
       </c>
       <c r="D72" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E72" s="1">
-        <v>516</v>
+        <v>642</v>
       </c>
       <c r="F72" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G72" s="1">
         <v>0</v>
       </c>
       <c r="H72" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="B73" s="2">
-        <v>0.3203479945659638</v>
+        <v>0.274141401052475</v>
       </c>
       <c r="C73" s="1">
-        <v>542</v>
+        <v>614</v>
       </c>
       <c r="D73" s="1">
-        <v>4</v>
+        <v>3202</v>
       </c>
       <c r="E73" s="1">
-        <v>542</v>
+        <v>614</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -5271,79 +5711,79 @@
         <v>0</v>
       </c>
       <c r="H73" s="1">
-        <v>4</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="B74" s="2">
-        <v>0.2990702688694</v>
+        <v>0.274141401052475</v>
       </c>
       <c r="C74" s="1">
-        <v>506</v>
+        <v>614</v>
       </c>
       <c r="D74" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>506</v>
+        <v>432</v>
       </c>
       <c r="F74" s="1">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="G74" s="1">
         <v>0</v>
       </c>
       <c r="H74" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="B75" s="2">
-        <v>0.2766104638576508</v>
+        <v>0.2714625000953674</v>
       </c>
       <c r="C75" s="1">
-        <v>468</v>
+        <v>608</v>
       </c>
       <c r="D75" s="1">
-        <v>24576</v>
+        <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>64</v>
+        <v>608</v>
       </c>
       <c r="F75" s="1">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="G75" s="1">
         <v>0</v>
       </c>
       <c r="H75" s="1">
-        <v>24576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B76" s="2">
-        <v>0.2706999778747559</v>
+        <v>0.2661046981811523</v>
       </c>
       <c r="C76" s="1">
-        <v>458</v>
+        <v>596</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>458</v>
+        <v>428</v>
       </c>
       <c r="F76" s="1">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
@@ -5354,45 +5794,45 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="B77" s="2">
-        <v>0.2671536803245544</v>
+        <v>0.2598538994789124</v>
       </c>
       <c r="C77" s="1">
-        <v>452</v>
+        <v>582</v>
       </c>
       <c r="D77" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E77" s="1">
-        <v>424</v>
+        <v>580</v>
       </c>
       <c r="F77" s="1">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G77" s="1">
         <v>0</v>
       </c>
       <c r="H77" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="B78" s="2">
-        <v>0.2636074125766754</v>
+        <v>0.2464593797922134</v>
       </c>
       <c r="C78" s="1">
-        <v>446</v>
+        <v>552</v>
       </c>
       <c r="D78" s="1">
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="E78" s="1">
-        <v>446</v>
+        <v>552</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -5401,27 +5841,27 @@
         <v>0</v>
       </c>
       <c r="H78" s="1">
-        <v>0</v>
+        <v>528</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B79" s="2">
-        <v>0.2588790059089661</v>
+        <v>0.2428874969482422</v>
       </c>
       <c r="C79" s="1">
-        <v>438</v>
+        <v>544</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
       </c>
       <c r="E79" s="1">
-        <v>438</v>
+        <v>516</v>
       </c>
       <c r="F79" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G79" s="1">
         <v>0</v>
@@ -5432,45 +5872,45 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B80" s="2">
-        <v>0.239965483546257</v>
+        <v>0.2419945299625397</v>
       </c>
       <c r="C80" s="1">
-        <v>406</v>
+        <v>542</v>
       </c>
       <c r="D80" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E80" s="1">
-        <v>350</v>
+        <v>542</v>
       </c>
       <c r="F80" s="1">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G80" s="1">
         <v>0</v>
       </c>
       <c r="H80" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B81" s="2">
-        <v>0.2352370917797089</v>
+        <v>0.225921094417572</v>
       </c>
       <c r="C81" s="1">
-        <v>398</v>
+        <v>506</v>
       </c>
       <c r="D81" s="1">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="E81" s="1">
-        <v>398</v>
+        <v>506</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -5479,76 +5919,76 @@
         <v>0</v>
       </c>
       <c r="H81" s="1">
-        <v>336</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="B82" s="2">
-        <v>0.2127772718667984</v>
+        <v>0.2089546918869019</v>
       </c>
       <c r="C82" s="1">
-        <v>360</v>
+        <v>468</v>
       </c>
       <c r="D82" s="1">
-        <v>0</v>
+        <v>24576</v>
       </c>
       <c r="E82" s="1">
-        <v>360</v>
+        <v>64</v>
       </c>
       <c r="F82" s="1">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
       </c>
       <c r="H82" s="1">
-        <v>0</v>
+        <v>24576</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="B83" s="2">
-        <v>0.2115951776504517</v>
+        <v>0.2049363255500794</v>
       </c>
       <c r="C83" s="1">
-        <v>358</v>
+        <v>459</v>
       </c>
       <c r="D83" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E83" s="1">
-        <v>358</v>
+        <v>444</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
       </c>
       <c r="G83" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H83" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="B84" s="2">
-        <v>0.2021384090185165</v>
+        <v>0.2044898420572281</v>
       </c>
       <c r="C84" s="1">
-        <v>342</v>
+        <v>458</v>
       </c>
       <c r="D84" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E84" s="1">
-        <v>342</v>
+        <v>458</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -5557,27 +5997,27 @@
         <v>0</v>
       </c>
       <c r="H84" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B85" s="2">
-        <v>0.1891353577375412</v>
+        <v>0.2018109411001205</v>
       </c>
       <c r="C85" s="1">
-        <v>320</v>
+        <v>452</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
       </c>
       <c r="E85" s="1">
-        <v>320</v>
+        <v>424</v>
       </c>
       <c r="F85" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G85" s="1">
         <v>0</v>
@@ -5588,19 +6028,19 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B86" s="2">
-        <v>0.1477620005607605</v>
+        <v>0.199132040143013</v>
       </c>
       <c r="C86" s="1">
-        <v>250</v>
+        <v>446</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>250</v>
+        <v>446</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -5614,19 +6054,19 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B87" s="2">
-        <v>0.1465799063444138</v>
+        <v>0.1955601572990418</v>
       </c>
       <c r="C87" s="1">
-        <v>248</v>
+        <v>438</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
       </c>
       <c r="E87" s="1">
-        <v>248</v>
+        <v>438</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -5640,45 +6080,45 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="B88" s="2">
-        <v>0.145397812128067</v>
+        <v>0.1812726557254791</v>
       </c>
       <c r="C88" s="1">
-        <v>246</v>
+        <v>406</v>
       </c>
       <c r="D88" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E88" s="1">
-        <v>246</v>
+        <v>350</v>
       </c>
       <c r="F88" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G88" s="1">
         <v>0</v>
       </c>
       <c r="H88" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="B89" s="2">
-        <v>0.1418515145778656</v>
+        <v>0.1777007877826691</v>
       </c>
       <c r="C89" s="1">
-        <v>240</v>
+        <v>398</v>
       </c>
       <c r="D89" s="1">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="E89" s="1">
-        <v>240</v>
+        <v>398</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -5687,24 +6127,24 @@
         <v>0</v>
       </c>
       <c r="H89" s="1">
-        <v>0</v>
+        <v>336</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="B90" s="2">
-        <v>0.1371231377124786</v>
+        <v>0.1607343703508377</v>
       </c>
       <c r="C90" s="1">
-        <v>232</v>
+        <v>360</v>
       </c>
       <c r="D90" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E90" s="1">
-        <v>232</v>
+        <v>360</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -5713,24 +6153,24 @@
         <v>0</v>
       </c>
       <c r="H90" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B91" s="2">
-        <v>0.1146633103489876</v>
+        <v>0.1598414033651352</v>
       </c>
       <c r="C91" s="1">
-        <v>194</v>
+        <v>358</v>
       </c>
       <c r="D91" s="1">
         <v>0</v>
       </c>
       <c r="E91" s="1">
-        <v>194</v>
+        <v>358</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
@@ -5744,45 +6184,45 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B92" s="2">
-        <v>0.1111170202493668</v>
+        <v>0.1526976525783539</v>
       </c>
       <c r="C92" s="1">
-        <v>188</v>
+        <v>342</v>
       </c>
       <c r="D92" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E92" s="1">
-        <v>180</v>
+        <v>342</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
       </c>
       <c r="G92" s="1">
+        <v>0</v>
+      </c>
+      <c r="H92" s="1">
         <v>8</v>
-      </c>
-      <c r="H92" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B93" s="2">
-        <v>0.1063886359333992</v>
+        <v>0.1518046855926514</v>
       </c>
       <c r="C93" s="1">
-        <v>180</v>
+        <v>340</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
       </c>
       <c r="E93" s="1">
-        <v>180</v>
+        <v>340</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -5796,45 +6236,45 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1" t="s">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="B94" s="2">
-        <v>0.1046154946088791</v>
+        <v>0.14108906686306</v>
       </c>
       <c r="C94" s="1">
-        <v>177</v>
+        <v>316</v>
       </c>
       <c r="D94" s="1">
-        <v>3309</v>
+        <v>0</v>
       </c>
       <c r="E94" s="1">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F94" s="1">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="G94" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" s="1">
-        <v>3308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B95" s="2">
-        <v>0.1016602516174316</v>
+        <v>0.1116210967302322</v>
       </c>
       <c r="C95" s="1">
-        <v>172</v>
+        <v>250</v>
       </c>
       <c r="D95" s="1">
         <v>0</v>
       </c>
       <c r="E95" s="1">
-        <v>172</v>
+        <v>250</v>
       </c>
       <c r="F95" s="1">
         <v>0</v>
@@ -5848,19 +6288,19 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B96" s="2">
-        <v>0.1004781574010849</v>
+        <v>0.1107281297445297</v>
       </c>
       <c r="C96" s="1">
-        <v>170</v>
+        <v>248</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
       </c>
       <c r="E96" s="1">
-        <v>170</v>
+        <v>248</v>
       </c>
       <c r="F96" s="1">
         <v>0</v>
@@ -5874,45 +6314,45 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1" t="s">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="B97" s="2">
-        <v>0.09929606318473816</v>
+        <v>0.1098351553082466</v>
       </c>
       <c r="C97" s="1">
-        <v>168</v>
+        <v>246</v>
       </c>
       <c r="D97" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>140</v>
+        <v>246</v>
       </c>
       <c r="F97" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G97" s="1">
         <v>0</v>
       </c>
       <c r="H97" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="B98" s="2">
-        <v>0.09693186730146408</v>
+        <v>0.1071562543511391</v>
       </c>
       <c r="C98" s="1">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="D98" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E98" s="1">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
@@ -5921,50 +6361,50 @@
         <v>0</v>
       </c>
       <c r="H98" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="B99" s="2">
-        <v>0.08747509866952896</v>
+        <v>0.1071562543511391</v>
       </c>
       <c r="C99" s="1">
-        <v>148</v>
+        <v>240</v>
       </c>
       <c r="D99" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="F99" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G99" s="1">
         <v>0</v>
       </c>
       <c r="H99" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="B100" s="2">
-        <v>0.08156462013721466</v>
+        <v>0.1035843789577484</v>
       </c>
       <c r="C100" s="1">
-        <v>138</v>
+        <v>232</v>
       </c>
       <c r="D100" s="1">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E100" s="1">
-        <v>138</v>
+        <v>232</v>
       </c>
       <c r="F100" s="1">
         <v>0</v>
@@ -5973,24 +6413,24 @@
         <v>0</v>
       </c>
       <c r="H100" s="1">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B101" s="2">
-        <v>0.07801833748817444</v>
+        <v>0.08661796897649765</v>
       </c>
       <c r="C101" s="1">
-        <v>132</v>
+        <v>194</v>
       </c>
       <c r="D101" s="1">
         <v>0</v>
       </c>
       <c r="E101" s="1">
-        <v>132</v>
+        <v>194</v>
       </c>
       <c r="F101" s="1">
         <v>0</v>
@@ -6004,45 +6444,45 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="B102" s="2">
-        <v>0.07328995317220688</v>
+        <v>0.08393906056880951</v>
       </c>
       <c r="C102" s="1">
-        <v>124</v>
+        <v>188</v>
       </c>
       <c r="D102" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E102" s="1">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
       </c>
       <c r="G102" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H102" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
-        <v>14</v>
+        <v>112</v>
       </c>
       <c r="B103" s="2">
-        <v>0.06856156885623932</v>
+        <v>0.08036718517541885</v>
       </c>
       <c r="C103" s="1">
-        <v>116</v>
+        <v>180</v>
       </c>
       <c r="D103" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E103" s="1">
-        <v>116</v>
+        <v>180</v>
       </c>
       <c r="F103" s="1">
         <v>0</v>
@@ -6051,50 +6491,50 @@
         <v>0</v>
       </c>
       <c r="H103" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
       <c r="B104" s="2">
-        <v>0.06856156885623932</v>
+        <v>0.07902773469686508</v>
       </c>
       <c r="C104" s="1">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="D104" s="1">
-        <v>0</v>
+        <v>3309</v>
       </c>
       <c r="E104" s="1">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="F104" s="1">
         <v>0</v>
       </c>
       <c r="G104" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" s="1">
-        <v>0</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B105" s="2">
-        <v>0.06619737297296524</v>
+        <v>0.0767953172326088</v>
       </c>
       <c r="C105" s="1">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="D105" s="1">
         <v>0</v>
       </c>
       <c r="E105" s="1">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="F105" s="1">
         <v>0</v>
@@ -6108,45 +6548,45 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="B106" s="2">
-        <v>0.06619737297296524</v>
+        <v>0.07500937581062317</v>
       </c>
       <c r="C106" s="1">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="D106" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E106" s="1">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="F106" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G106" s="1">
         <v>0</v>
       </c>
       <c r="H106" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1" t="s">
-        <v>109</v>
+        <v>10</v>
       </c>
       <c r="B107" s="2">
-        <v>0.06619737297296524</v>
+        <v>0.07322344183921814</v>
       </c>
       <c r="C107" s="1">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="D107" s="1">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="E107" s="1">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="F107" s="1">
         <v>0</v>
@@ -6155,24 +6595,24 @@
         <v>0</v>
       </c>
       <c r="H107" s="1">
-        <v>0</v>
+        <v>256</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B108" s="2">
-        <v>0.0591048002243042</v>
+        <v>0.07143750041723251</v>
       </c>
       <c r="C108" s="1">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
       </c>
       <c r="E108" s="1">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="F108" s="1">
         <v>0</v>
@@ -6186,19 +6626,19 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B109" s="2">
-        <v>0.05555851012468338</v>
+        <v>0.07054453343153</v>
       </c>
       <c r="C109" s="1">
-        <v>94</v>
+        <v>158</v>
       </c>
       <c r="D109" s="1">
         <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>94</v>
+        <v>158</v>
       </c>
       <c r="F109" s="1">
         <v>0</v>
@@ -6212,19 +6652,19 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B110" s="2">
-        <v>0.05083012580871582</v>
+        <v>0.06965156644582748</v>
       </c>
       <c r="C110" s="1">
-        <v>86</v>
+        <v>156</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
       </c>
       <c r="E110" s="1">
-        <v>86</v>
+        <v>156</v>
       </c>
       <c r="F110" s="1">
         <v>0</v>
@@ -6238,45 +6678,45 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="B111" s="2">
-        <v>0.04964803159236908</v>
+        <v>0.06607969105243683</v>
       </c>
       <c r="C111" s="1">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="D111" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E111" s="1">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F111" s="1">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="G111" s="1">
         <v>0</v>
       </c>
       <c r="H111" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B112" s="2">
-        <v>0.04610174149274826</v>
+        <v>0.06161484494805336</v>
       </c>
       <c r="C112" s="1">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="D112" s="1">
         <v>0</v>
       </c>
       <c r="E112" s="1">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
@@ -6290,22 +6730,22 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B113" s="2">
-        <v>0.04610174149274826</v>
+        <v>0.05982890725135803</v>
       </c>
       <c r="C113" s="1">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="D113" s="1">
         <v>0</v>
       </c>
       <c r="E113" s="1">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="F113" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G113" s="1">
         <v>0</v>
@@ -6316,19 +6756,19 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B114" s="2">
-        <v>0.04373754933476448</v>
+        <v>0.05536406487226486</v>
       </c>
       <c r="C114" s="1">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
       </c>
       <c r="E114" s="1">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="F114" s="1">
         <v>0</v>
@@ -6342,45 +6782,45 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="B115" s="2">
-        <v>0.04255545511841774</v>
+        <v>0.05179218947887421</v>
       </c>
       <c r="C115" s="1">
+        <v>116</v>
+      </c>
+      <c r="D115" s="1">
         <v>72</v>
       </c>
-      <c r="D115" s="1">
-        <v>0</v>
-      </c>
       <c r="E115" s="1">
+        <v>116</v>
+      </c>
+      <c r="F115" s="1">
+        <v>0</v>
+      </c>
+      <c r="G115" s="1">
+        <v>0</v>
+      </c>
+      <c r="H115" s="1">
         <v>72</v>
-      </c>
-      <c r="F115" s="1">
-        <v>0</v>
-      </c>
-      <c r="G115" s="1">
-        <v>0</v>
-      </c>
-      <c r="H115" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B116" s="2">
-        <v>0.03782707080245018</v>
+        <v>0.05179218947887421</v>
       </c>
       <c r="C116" s="1">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="D116" s="1">
         <v>0</v>
       </c>
       <c r="E116" s="1">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -6394,19 +6834,19 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B117" s="2">
-        <v>0.03782707080245018</v>
+        <v>0.05000625178217888</v>
       </c>
       <c r="C117" s="1">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="D117" s="1">
         <v>0</v>
       </c>
       <c r="E117" s="1">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
@@ -6420,19 +6860,19 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B118" s="2">
-        <v>0.03664497658610344</v>
+        <v>0.05000625178217888</v>
       </c>
       <c r="C118" s="1">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="D118" s="1">
         <v>0</v>
       </c>
       <c r="E118" s="1">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="F118" s="1">
         <v>0</v>
@@ -6446,19 +6886,19 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B119" s="2">
-        <v>0.03309868648648262</v>
+        <v>0.0446484386920929</v>
       </c>
       <c r="C119" s="1">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="D119" s="1">
         <v>0</v>
       </c>
       <c r="E119" s="1">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="F119" s="1">
         <v>0</v>
@@ -6472,22 +6912,22 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B120" s="2">
-        <v>0.03309868648648262</v>
+        <v>0.04196953028440476</v>
       </c>
       <c r="C120" s="1">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D120" s="1">
         <v>0</v>
       </c>
       <c r="E120" s="1">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F120" s="1">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G120" s="1">
         <v>0</v>
@@ -6498,19 +6938,19 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B121" s="2">
-        <v>0.03073449619114399</v>
+        <v>0.04196953028440476</v>
       </c>
       <c r="C121" s="1">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="D121" s="1">
         <v>0</v>
       </c>
       <c r="E121" s="1">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="F121" s="1">
         <v>0</v>
@@ -6524,19 +6964,19 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="B122" s="2">
-        <v>0.02837030403316021</v>
+        <v>0.0383976586163044</v>
       </c>
       <c r="C122" s="1">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="D122" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E122" s="1">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="F122" s="1">
         <v>0</v>
@@ -6545,27 +6985,27 @@
         <v>0</v>
       </c>
       <c r="H122" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B123" s="2">
-        <v>0.02718820795416832</v>
+        <v>0.03750468790531158</v>
       </c>
       <c r="C123" s="1">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="D123" s="1">
         <v>0</v>
       </c>
       <c r="E123" s="1">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F123" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G123" s="1">
         <v>0</v>
@@ -6576,25 +7016,25 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1" t="s">
-        <v>35</v>
+        <v>128</v>
       </c>
       <c r="B124" s="2">
-        <v>0.02600611187517643</v>
+        <v>0.03482578322291374</v>
       </c>
       <c r="C124" s="1">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="D124" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E124" s="1">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="F124" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G124" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H124" s="1">
         <v>0</v>
@@ -6602,22 +7042,22 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B125" s="2">
-        <v>0.01654934324324131</v>
+        <v>0.03482578322291374</v>
       </c>
       <c r="C125" s="1">
+        <v>78</v>
+      </c>
+      <c r="D125" s="1">
+        <v>0</v>
+      </c>
+      <c r="E125" s="1">
+        <v>50</v>
+      </c>
+      <c r="F125" s="1">
         <v>28</v>
-      </c>
-      <c r="D125" s="1">
-        <v>0</v>
-      </c>
-      <c r="E125" s="1">
-        <v>28</v>
-      </c>
-      <c r="F125" s="1">
-        <v>0</v>
       </c>
       <c r="G125" s="1">
         <v>0</v>
@@ -6628,19 +7068,19 @@
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B126" s="2">
-        <v>0.015367248095572</v>
+        <v>0.03303984552621841</v>
       </c>
       <c r="C126" s="1">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="D126" s="1">
         <v>0</v>
       </c>
       <c r="E126" s="1">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
@@ -6654,19 +7094,19 @@
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B127" s="2">
-        <v>0.015367248095572</v>
+        <v>0.0321468748152256</v>
       </c>
       <c r="C127" s="1">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
       </c>
       <c r="E127" s="1">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="F127" s="1">
         <v>0</v>
@@ -6680,25 +7120,25 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1" t="s">
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="B128" s="2">
-        <v>0.015367248095572</v>
+        <v>0.03080742247402668</v>
       </c>
       <c r="C128" s="1">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="D128" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" s="1">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
       </c>
       <c r="G128" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H128" s="1">
         <v>0</v>
@@ -6706,19 +7146,19 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B129" s="2">
-        <v>0.01063886377960444</v>
+        <v>0.03036093711853027</v>
       </c>
       <c r="C129" s="1">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="D129" s="1">
         <v>0</v>
       </c>
       <c r="E129" s="1">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="F129" s="1">
         <v>0</v>
@@ -6732,19 +7172,19 @@
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B130" s="2">
-        <v>0.009456767700612545</v>
+        <v>0.0285750012844801</v>
       </c>
       <c r="C130" s="1">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D130" s="1">
         <v>0</v>
       </c>
       <c r="E130" s="1">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="F130" s="1">
         <v>0</v>
@@ -6758,19 +7198,19 @@
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B131" s="2">
-        <v>0.009456767700612545</v>
+        <v>0.0285750012844801</v>
       </c>
       <c r="C131" s="1">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D131" s="1">
         <v>0</v>
       </c>
       <c r="E131" s="1">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="F131" s="1">
         <v>0</v>
@@ -6784,19 +7224,19 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B132" s="2">
-        <v>0.008274671621620655</v>
+        <v>0.02768203243613243</v>
       </c>
       <c r="C132" s="1">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="D132" s="1">
         <v>0</v>
       </c>
       <c r="E132" s="1">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="F132" s="1">
         <v>0</v>
@@ -6810,19 +7250,19 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B133" s="2">
-        <v>0.007092576008290052</v>
+        <v>0.02500312589108944</v>
       </c>
       <c r="C133" s="1">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="D133" s="1">
         <v>0</v>
       </c>
       <c r="E133" s="1">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="F133" s="1">
         <v>0</v>
@@ -6836,22 +7276,22 @@
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B134" s="2">
-        <v>0.007092576008290052</v>
+        <v>0.02500312589108944</v>
       </c>
       <c r="C134" s="1">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="D134" s="1">
         <v>0</v>
       </c>
       <c r="E134" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F134" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G134" s="1">
         <v>0</v>
@@ -6862,19 +7302,19 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B135" s="2">
-        <v>0.005910479929298163</v>
+        <v>0.02321718819439411</v>
       </c>
       <c r="C135" s="1">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="D135" s="1">
         <v>0</v>
       </c>
       <c r="E135" s="1">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
@@ -6888,19 +7328,19 @@
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="1" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="B136" s="2">
-        <v>0.005910479929298163</v>
+        <v>0.02143125049769878</v>
       </c>
       <c r="C136" s="1">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D136" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E136" s="1">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="F136" s="1">
         <v>0</v>
@@ -6909,24 +7349,24 @@
         <v>0</v>
       </c>
       <c r="H136" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="B137" s="2">
-        <v>0.004728383850306273</v>
+        <v>0.02053828164935112</v>
       </c>
       <c r="C137" s="1">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="D137" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E137" s="1">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="F137" s="1">
         <v>0</v>
@@ -6935,24 +7375,24 @@
         <v>0</v>
       </c>
       <c r="H137" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B138" s="2">
-        <v>0.004728383850306273</v>
+        <v>0.02053828164935112</v>
       </c>
       <c r="C138" s="1">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="D138" s="1">
         <v>0</v>
       </c>
       <c r="E138" s="1">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="F138" s="1">
         <v>0</v>
@@ -6966,25 +7406,25 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="1" t="s">
-        <v>138</v>
+        <v>41</v>
       </c>
       <c r="B139" s="2">
-        <v>0.003546288004145026</v>
+        <v>0.01964531280100346</v>
       </c>
       <c r="C139" s="1">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D139" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E139" s="1">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F139" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G139" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H139" s="1">
         <v>0</v>
@@ -6992,19 +7432,19 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B140" s="2">
-        <v>0.003546288004145026</v>
+        <v>0.01428750064224005</v>
       </c>
       <c r="C140" s="1">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D140" s="1">
         <v>0</v>
       </c>
       <c r="E140" s="1">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F140" s="1">
         <v>0</v>
@@ -7018,19 +7458,19 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B141" s="2">
-        <v>0.003546288004145026</v>
+        <v>0.01250156294554472</v>
       </c>
       <c r="C141" s="1">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D141" s="1">
         <v>0</v>
       </c>
       <c r="E141" s="1">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F141" s="1">
         <v>0</v>
@@ -7044,19 +7484,19 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B142" s="2">
-        <v>0.002364191925153136</v>
+        <v>0.01250156294554472</v>
       </c>
       <c r="C142" s="1">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D142" s="1">
         <v>0</v>
       </c>
       <c r="E142" s="1">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F142" s="1">
         <v>0</v>
@@ -7070,19 +7510,19 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B143" s="2">
-        <v>0.001182095962576568</v>
+        <v>0.01250156294554472</v>
       </c>
       <c r="C143" s="1">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D143" s="1">
         <v>0</v>
       </c>
       <c r="E143" s="1">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F143" s="1">
         <v>0</v>
@@ -7096,19 +7536,19 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B144" s="2">
-        <v>0.001182095962576568</v>
+        <v>0.01160859409719706</v>
       </c>
       <c r="C144" s="1">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D144" s="1">
         <v>0</v>
       </c>
       <c r="E144" s="1">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="F144" s="1">
         <v>0</v>
@@ -7122,19 +7562,19 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B145" s="2">
-        <v>0.001182095962576568</v>
+        <v>0.01160859409719706</v>
       </c>
       <c r="C145" s="1">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D145" s="1">
         <v>0</v>
       </c>
       <c r="E145" s="1">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="F145" s="1">
         <v>0</v>
@@ -7148,19 +7588,19 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B146" s="2">
-        <v>0.001182095962576568</v>
+        <v>0.01160859409719706</v>
       </c>
       <c r="C146" s="1">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D146" s="1">
         <v>0</v>
       </c>
       <c r="E146" s="1">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="F146" s="1">
         <v>0</v>
@@ -7174,59 +7614,683 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B147" s="2">
-        <v>0.001182095962576568</v>
+        <v>0.01071562524884939</v>
       </c>
       <c r="C147" s="1">
+        <v>24</v>
+      </c>
+      <c r="D147" s="1">
+        <v>0</v>
+      </c>
+      <c r="E147" s="1">
+        <v>24</v>
+      </c>
+      <c r="F147" s="1">
+        <v>0</v>
+      </c>
+      <c r="G147" s="1">
+        <v>0</v>
+      </c>
+      <c r="H147" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B148" s="2">
+        <v>0.01071562524884939</v>
+      </c>
+      <c r="C148" s="1">
+        <v>24</v>
+      </c>
+      <c r="D148" s="1">
+        <v>0</v>
+      </c>
+      <c r="E148" s="1">
+        <v>24</v>
+      </c>
+      <c r="F148" s="1">
+        <v>0</v>
+      </c>
+      <c r="G148" s="1">
+        <v>0</v>
+      </c>
+      <c r="H148" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B149" s="2">
+        <v>0.0080367187038064</v>
+      </c>
+      <c r="C149" s="1">
+        <v>18</v>
+      </c>
+      <c r="D149" s="1">
+        <v>0</v>
+      </c>
+      <c r="E149" s="1">
+        <v>18</v>
+      </c>
+      <c r="F149" s="1">
+        <v>0</v>
+      </c>
+      <c r="G149" s="1">
+        <v>0</v>
+      </c>
+      <c r="H149" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B150" s="2">
+        <v>0.007143750321120024</v>
+      </c>
+      <c r="C150" s="1">
+        <v>16</v>
+      </c>
+      <c r="D150" s="1">
+        <v>4</v>
+      </c>
+      <c r="E150" s="1">
+        <v>12</v>
+      </c>
+      <c r="F150" s="1">
+        <v>0</v>
+      </c>
+      <c r="G150" s="1">
+        <v>4</v>
+      </c>
+      <c r="H150" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B151" s="2">
+        <v>0.007143750321120024</v>
+      </c>
+      <c r="C151" s="1">
+        <v>16</v>
+      </c>
+      <c r="D151" s="1">
+        <v>0</v>
+      </c>
+      <c r="E151" s="1">
+        <v>16</v>
+      </c>
+      <c r="F151" s="1">
+        <v>0</v>
+      </c>
+      <c r="G151" s="1">
+        <v>0</v>
+      </c>
+      <c r="H151" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B152" s="2">
+        <v>0.007143750321120024</v>
+      </c>
+      <c r="C152" s="1">
+        <v>16</v>
+      </c>
+      <c r="D152" s="1">
+        <v>0</v>
+      </c>
+      <c r="E152" s="1">
+        <v>16</v>
+      </c>
+      <c r="F152" s="1">
+        <v>0</v>
+      </c>
+      <c r="G152" s="1">
+        <v>0</v>
+      </c>
+      <c r="H152" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B153" s="2">
+        <v>0.007143750321120024</v>
+      </c>
+      <c r="C153" s="1">
+        <v>16</v>
+      </c>
+      <c r="D153" s="1">
+        <v>0</v>
+      </c>
+      <c r="E153" s="1">
+        <v>16</v>
+      </c>
+      <c r="F153" s="1">
+        <v>0</v>
+      </c>
+      <c r="G153" s="1">
+        <v>0</v>
+      </c>
+      <c r="H153" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B154" s="2">
+        <v>0.00625078147277236</v>
+      </c>
+      <c r="C154" s="1">
+        <v>14</v>
+      </c>
+      <c r="D154" s="1">
+        <v>0</v>
+      </c>
+      <c r="E154" s="1">
+        <v>14</v>
+      </c>
+      <c r="F154" s="1">
+        <v>0</v>
+      </c>
+      <c r="G154" s="1">
+        <v>0</v>
+      </c>
+      <c r="H154" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B155" s="2">
+        <v>0.005357812624424696</v>
+      </c>
+      <c r="C155" s="1">
+        <v>12</v>
+      </c>
+      <c r="D155" s="1">
+        <v>0</v>
+      </c>
+      <c r="E155" s="1">
+        <v>12</v>
+      </c>
+      <c r="F155" s="1">
+        <v>0</v>
+      </c>
+      <c r="G155" s="1">
+        <v>0</v>
+      </c>
+      <c r="H155" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B156" s="2">
+        <v>0.005357812624424696</v>
+      </c>
+      <c r="C156" s="1">
+        <v>12</v>
+      </c>
+      <c r="D156" s="1">
+        <v>0</v>
+      </c>
+      <c r="E156" s="1">
+        <v>12</v>
+      </c>
+      <c r="F156" s="1">
+        <v>0</v>
+      </c>
+      <c r="G156" s="1">
+        <v>0</v>
+      </c>
+      <c r="H156" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B157" s="2">
+        <v>0.005357812624424696</v>
+      </c>
+      <c r="C157" s="1">
+        <v>12</v>
+      </c>
+      <c r="D157" s="1">
+        <v>0</v>
+      </c>
+      <c r="E157" s="1">
+        <v>12</v>
+      </c>
+      <c r="F157" s="1">
+        <v>0</v>
+      </c>
+      <c r="G157" s="1">
+        <v>0</v>
+      </c>
+      <c r="H157" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B158" s="2">
+        <v>0.004464843776077032</v>
+      </c>
+      <c r="C158" s="1">
+        <v>10</v>
+      </c>
+      <c r="D158" s="1">
+        <v>0</v>
+      </c>
+      <c r="E158" s="1">
+        <v>10</v>
+      </c>
+      <c r="F158" s="1">
+        <v>0</v>
+      </c>
+      <c r="G158" s="1">
+        <v>0</v>
+      </c>
+      <c r="H158" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B159" s="2">
+        <v>0.004464843776077032</v>
+      </c>
+      <c r="C159" s="1">
+        <v>10</v>
+      </c>
+      <c r="D159" s="1">
+        <v>0</v>
+      </c>
+      <c r="E159" s="1">
+        <v>10</v>
+      </c>
+      <c r="F159" s="1">
+        <v>0</v>
+      </c>
+      <c r="G159" s="1">
+        <v>0</v>
+      </c>
+      <c r="H159" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B160" s="2">
+        <v>0.003571875160560012</v>
+      </c>
+      <c r="C160" s="1">
+        <v>8</v>
+      </c>
+      <c r="D160" s="1">
+        <v>0</v>
+      </c>
+      <c r="E160" s="1">
+        <v>8</v>
+      </c>
+      <c r="F160" s="1">
+        <v>0</v>
+      </c>
+      <c r="G160" s="1">
+        <v>0</v>
+      </c>
+      <c r="H160" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B161" s="2">
+        <v>0.003571875160560012</v>
+      </c>
+      <c r="C161" s="1">
+        <v>8</v>
+      </c>
+      <c r="D161" s="1">
+        <v>0</v>
+      </c>
+      <c r="E161" s="1">
+        <v>8</v>
+      </c>
+      <c r="F161" s="1">
+        <v>0</v>
+      </c>
+      <c r="G161" s="1">
+        <v>0</v>
+      </c>
+      <c r="H161" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B162" s="2">
+        <v>0.003571875160560012</v>
+      </c>
+      <c r="C162" s="1">
+        <v>8</v>
+      </c>
+      <c r="D162" s="1">
+        <v>96</v>
+      </c>
+      <c r="E162" s="1">
+        <v>8</v>
+      </c>
+      <c r="F162" s="1">
+        <v>0</v>
+      </c>
+      <c r="G162" s="1">
+        <v>0</v>
+      </c>
+      <c r="H162" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2">
+        <v>0.003571875160560012</v>
+      </c>
+      <c r="C163" s="1">
+        <v>8</v>
+      </c>
+      <c r="D163" s="1">
+        <v>0</v>
+      </c>
+      <c r="E163" s="1">
+        <v>8</v>
+      </c>
+      <c r="F163" s="1">
+        <v>0</v>
+      </c>
+      <c r="G163" s="1">
+        <v>0</v>
+      </c>
+      <c r="H163" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2">
+        <v>0.002678906312212348</v>
+      </c>
+      <c r="C164" s="1">
+        <v>6</v>
+      </c>
+      <c r="D164" s="1">
+        <v>0</v>
+      </c>
+      <c r="E164" s="1">
+        <v>6</v>
+      </c>
+      <c r="F164" s="1">
+        <v>0</v>
+      </c>
+      <c r="G164" s="1">
+        <v>0</v>
+      </c>
+      <c r="H164" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2">
+        <v>0.002678906312212348</v>
+      </c>
+      <c r="C165" s="1">
+        <v>6</v>
+      </c>
+      <c r="D165" s="1">
+        <v>0</v>
+      </c>
+      <c r="E165" s="1">
+        <v>6</v>
+      </c>
+      <c r="F165" s="1">
+        <v>0</v>
+      </c>
+      <c r="G165" s="1">
+        <v>0</v>
+      </c>
+      <c r="H165" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2">
+        <v>0.001785937580280006</v>
+      </c>
+      <c r="C166" s="1">
+        <v>4</v>
+      </c>
+      <c r="D166" s="1">
+        <v>0</v>
+      </c>
+      <c r="E166" s="1">
+        <v>4</v>
+      </c>
+      <c r="F166" s="1">
+        <v>0</v>
+      </c>
+      <c r="G166" s="1">
+        <v>0</v>
+      </c>
+      <c r="H166" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2">
+        <v>0.000892968790140003</v>
+      </c>
+      <c r="C167" s="1">
         <v>2</v>
       </c>
-      <c r="D147" s="1">
-        <v>0</v>
-      </c>
-      <c r="E147" s="1">
+      <c r="D167" s="1">
+        <v>0</v>
+      </c>
+      <c r="E167" s="1">
         <v>2</v>
       </c>
-      <c r="F147" s="1">
-        <v>0</v>
-      </c>
-      <c r="G147" s="1">
-        <v>0</v>
-      </c>
-      <c r="H147" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8">
-      <c r="A148" t="s">
-        <v>148</v>
-      </c>
-      <c r="B148">
+      <c r="F167" s="1">
+        <v>0</v>
+      </c>
+      <c r="G167" s="1">
+        <v>0</v>
+      </c>
+      <c r="H167" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2">
+        <v>0.000892968790140003</v>
+      </c>
+      <c r="C168" s="1">
+        <v>2</v>
+      </c>
+      <c r="D168" s="1">
+        <v>0</v>
+      </c>
+      <c r="E168" s="1">
+        <v>2</v>
+      </c>
+      <c r="F168" s="1">
+        <v>0</v>
+      </c>
+      <c r="G168" s="1">
+        <v>0</v>
+      </c>
+      <c r="H168" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2">
+        <v>0.000892968790140003</v>
+      </c>
+      <c r="C169" s="1">
+        <v>2</v>
+      </c>
+      <c r="D169" s="1">
+        <v>0</v>
+      </c>
+      <c r="E169" s="1">
+        <v>2</v>
+      </c>
+      <c r="F169" s="1">
+        <v>0</v>
+      </c>
+      <c r="G169" s="1">
+        <v>0</v>
+      </c>
+      <c r="H169" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2">
+        <v>0.000892968790140003</v>
+      </c>
+      <c r="C170" s="1">
+        <v>2</v>
+      </c>
+      <c r="D170" s="1">
+        <v>0</v>
+      </c>
+      <c r="E170" s="1">
+        <v>2</v>
+      </c>
+      <c r="F170" s="1">
+        <v>0</v>
+      </c>
+      <c r="G170" s="1">
+        <v>0</v>
+      </c>
+      <c r="H170" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2">
+        <v>0.000892968790140003</v>
+      </c>
+      <c r="C171" s="1">
+        <v>2</v>
+      </c>
+      <c r="D171" s="1">
+        <v>0</v>
+      </c>
+      <c r="E171" s="1">
+        <v>2</v>
+      </c>
+      <c r="F171" s="1">
+        <v>0</v>
+      </c>
+      <c r="G171" s="1">
+        <v>0</v>
+      </c>
+      <c r="H171" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" t="s">
+        <v>172</v>
+      </c>
+      <c r="B172">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C148">
+      <c r="C172">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D148">
+      <c r="D172">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E148">
+      <c r="E172">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F148">
+      <c r="F172">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G148">
+      <c r="G172">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H148">
+      <c r="H172">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
